--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50AB62B-4423-4C64-B4F1-08F4397206FF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC7D183-7C25-4AC3-A241-52FD330D4F61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$66</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$68</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="393">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -314,10 +314,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>포천 차우면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>철원 갈말읍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -750,10 +746,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>모돈 4두 폐사(1.22~23) 다수 식욕부진</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>모돈 12두 폐사(1.23~24)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1286,10 +1278,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>자돈 질병 진단 의뢰 가검물서 양서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>자돈 폐사 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1499,6 +1487,54 @@
   </si>
   <si>
     <t>62번</t>
+  </si>
+  <si>
+    <t>63번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>64번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>포천 관인면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화성 남양읍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후보돈 5두, 비육돈 7두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>출하 전 검사 양성 1두 검출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자돈 질병 진단 의뢰 가검물서 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모돈 4두 폐사(1.22~23), 다수 식욕부진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2221,7 +2257,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2237,7 +2273,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.6" x14ac:dyDescent="0.4">
       <c r="A1" s="36" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -2252,13 +2288,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E2" s="33" t="s">
         <v>1</v>
@@ -2270,15 +2306,15 @@
         <v>3</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>5</v>
@@ -2287,24 +2323,24 @@
         <v>37</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G3" s="5">
         <v>2369</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>6</v>
@@ -2313,24 +2349,24 @@
         <v>37</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G4" s="3">
         <v>4638</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>7</v>
@@ -2339,10 +2375,10 @@
         <v>37</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G5" s="3">
         <v>2119</v>
@@ -2353,10 +2389,10 @@
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="20" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>8</v>
@@ -2365,10 +2401,10 @@
         <v>37</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G6" s="3">
         <v>2273</v>
@@ -2379,10 +2415,10 @@
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="20" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>9</v>
@@ -2391,10 +2427,10 @@
         <v>37</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G7" s="3">
         <v>388</v>
@@ -2405,10 +2441,10 @@
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="20" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>10</v>
@@ -2417,10 +2453,10 @@
         <v>37</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G8" s="3">
         <v>869</v>
@@ -2431,10 +2467,10 @@
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="20" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>11</v>
@@ -2443,24 +2479,24 @@
         <v>37</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G9" s="3">
         <v>2</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="20" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>12</v>
@@ -2469,10 +2505,10 @@
         <v>37</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G10" s="3">
         <v>1125</v>
@@ -2483,10 +2519,10 @@
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="20" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="9" t="s">
         <v>13</v>
@@ -2495,10 +2531,10 @@
         <v>37</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G11" s="3">
         <v>2123</v>
@@ -2509,10 +2545,10 @@
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="20" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>14</v>
@@ -2521,10 +2557,10 @@
         <v>37</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>190</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>192</v>
       </c>
       <c r="G12" s="3">
         <v>2661</v>
@@ -2535,10 +2571,10 @@
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="20" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13" s="9" t="s">
         <v>15</v>
@@ -2547,10 +2583,10 @@
         <v>37</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G13" s="3">
         <v>19</v>
@@ -2561,10 +2597,10 @@
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="20" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>16</v>
@@ -2573,10 +2609,10 @@
         <v>37</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G14" s="3">
         <v>2267</v>
@@ -2587,10 +2623,10 @@
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="20" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" s="9" t="s">
         <v>17</v>
@@ -2599,10 +2635,10 @@
         <v>37</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G15" s="3">
         <v>2916</v>
@@ -2613,10 +2649,10 @@
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="20" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C16" s="9" t="s">
         <v>18</v>
@@ -2625,10 +2661,10 @@
         <v>37</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G16" s="3">
         <v>4245</v>
@@ -2639,10 +2675,10 @@
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="20" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C17" s="9" t="s">
         <v>19</v>
@@ -2651,10 +2687,10 @@
         <v>36</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G17" s="3">
         <v>726</v>
@@ -2665,10 +2701,10 @@
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="20" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C18" s="9" t="s">
         <v>20</v>
@@ -2677,10 +2713,10 @@
         <v>36</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G18" s="3">
         <v>1020</v>
@@ -2691,22 +2727,22 @@
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="20" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C19" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G19" s="3">
         <v>385</v>
@@ -2717,22 +2753,22 @@
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="20" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C20" s="9" t="s">
         <v>22</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G20" s="3">
         <v>2387</v>
@@ -2743,22 +2779,22 @@
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="20" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G21" s="3">
         <v>1801</v>
@@ -2769,22 +2805,22 @@
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="20" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C22" s="9" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G22" s="3">
         <v>2300</v>
@@ -2795,22 +2831,22 @@
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="20" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C23" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G23" s="3">
         <v>579</v>
@@ -2821,10 +2857,10 @@
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="20" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>26</v>
@@ -2833,10 +2869,10 @@
         <v>38</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F24" s="20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G24" s="3">
         <v>1175</v>
@@ -2847,10 +2883,10 @@
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="20" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>27</v>
@@ -2859,10 +2895,10 @@
         <v>38</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G25" s="3">
         <v>5614</v>
@@ -2873,10 +2909,10 @@
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="20" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>28</v>
@@ -2885,10 +2921,10 @@
         <v>38</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F26" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G26" s="3">
         <v>8243</v>
@@ -2899,10 +2935,10 @@
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="20" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>29</v>
@@ -2911,10 +2947,10 @@
         <v>38</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G27" s="3">
         <v>6824</v>
@@ -2925,10 +2961,10 @@
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="20" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C28" s="9" t="s">
         <v>30</v>
@@ -2937,10 +2973,10 @@
         <v>38</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G28" s="3">
         <v>5203</v>
@@ -2951,10 +2987,10 @@
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="20" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C29" s="9" t="s">
         <v>31</v>
@@ -2963,10 +2999,10 @@
         <v>38</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G29" s="3">
         <v>1133</v>
@@ -2977,10 +3013,10 @@
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="20" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C30" s="9" t="s">
         <v>32</v>
@@ -2989,10 +3025,10 @@
         <v>38</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G30" s="3">
         <v>5499</v>
@@ -3003,74 +3039,74 @@
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="20" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>33</v>
       </c>
       <c r="D31" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G31" s="3">
         <v>8094</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="20" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>34</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G32" s="3">
         <v>2369</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="20" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G33" s="3">
         <v>2009</v>
@@ -3081,22 +3117,22 @@
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="20" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>66</v>
       </c>
       <c r="D34" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G34" s="3">
         <v>1956</v>
@@ -3107,48 +3143,48 @@
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="20" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>68</v>
       </c>
       <c r="D35" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G35" s="3">
         <v>12842</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="20" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>69</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G36" s="3">
         <v>10218</v>
@@ -3159,22 +3195,22 @@
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="20" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>70</v>
       </c>
       <c r="D37" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G37" s="3">
         <v>9724</v>
@@ -3185,751 +3221,803 @@
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="20" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G38" s="3">
         <v>6118</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="20" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D39" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G39" s="3">
         <v>6077</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="20" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G40" s="3">
         <v>1246</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="20" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>88</v>
-      </c>
       <c r="E41" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G41" s="3">
         <v>499</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="20" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C42" s="20" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G42" s="3">
         <v>2375</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="20" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G43" s="3">
         <v>1577</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="20" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G44" s="3">
         <v>25900</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="20" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D45" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G45" s="3">
         <v>193</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="20" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G46" s="3">
         <v>1117</v>
       </c>
       <c r="H46" s="20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="20" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D47" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G47" s="3">
         <v>1927</v>
       </c>
       <c r="H47" s="20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="20" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D48" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G48" s="3">
         <v>4198</v>
       </c>
       <c r="H48" s="20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="20" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D49" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G49" s="3">
         <v>4277</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="20" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G50" s="3">
         <v>2733</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="20" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G51" s="3">
         <v>4950</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="20" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D52" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G52" s="3">
         <v>5232</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="20" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D53" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="F53" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G53" s="3">
         <v>4134</v>
       </c>
       <c r="H53" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="20" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D54" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G54" s="3">
         <v>5983</v>
       </c>
       <c r="H54" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="20" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B55" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C55" s="20" t="s">
         <v>163</v>
       </c>
-      <c r="C55" s="20" t="s">
-        <v>164</v>
-      </c>
       <c r="D55" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F55" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G55" s="3">
         <v>2465</v>
       </c>
       <c r="H55" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="29" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C56" s="20" t="s">
         <v>14</v>
       </c>
       <c r="D56" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G56" s="3">
         <v>8889</v>
       </c>
       <c r="H56" s="21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="20" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="G57" s="3">
         <v>847</v>
       </c>
       <c r="H57" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="20" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B58" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="C58" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="20" t="s">
-        <v>169</v>
-      </c>
       <c r="D58" s="20" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G58" s="3">
         <v>1423</v>
       </c>
       <c r="H58" s="21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="20" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B59" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D59" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G59" s="3">
         <v>20150</v>
       </c>
       <c r="H59" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="20" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D60" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G60" s="3">
         <v>2459</v>
       </c>
       <c r="H60" s="21" t="s">
-        <v>182</v>
+        <v>392</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="20" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B61" s="20" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D61" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G61" s="3">
         <v>7945</v>
       </c>
       <c r="H61" s="21" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="20" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B62" s="20" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D62" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G62" s="3">
-        <v>21000</v>
+        <v>21114</v>
       </c>
       <c r="H62" s="21" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="20" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B63" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="C63" s="20" t="s">
-        <v>307</v>
-      </c>
       <c r="D63" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G63" s="3">
-        <v>17658</v>
+        <v>18586</v>
       </c>
       <c r="H63" s="21" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="20" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B64" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D64" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G64" s="3">
-        <v>3500</v>
+        <v>4050</v>
       </c>
       <c r="H64" s="21" t="s">
-        <v>316</v>
+        <v>391</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="B65" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2562</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="20" t="s">
+        <v>381</v>
+      </c>
+      <c r="B66" s="20" t="s">
         <v>383</v>
       </c>
-      <c r="B65" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>309</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="G65" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="37" t="s">
+      <c r="C66" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="G66" s="3">
+        <v>8520</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="20" t="s">
+        <v>382</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="G67" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B66" s="38"/>
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="39"/>
-      <c r="G66" s="12">
-        <f>SUM(G3:G65)</f>
-        <v>285387</v>
-      </c>
-      <c r="H66" s="13"/>
+      <c r="B68" s="38"/>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="12">
+        <f>SUM(G3:G67)</f>
+        <v>296761</v>
+      </c>
+      <c r="H68" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A68:F68"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -3981,40 +4069,40 @@
     </row>
     <row r="3" spans="1:11" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="24" t="s">
+        <v>315</v>
+      </c>
+      <c r="H3" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="I3" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="J3" s="24" t="s">
         <v>137</v>
-      </c>
-      <c r="B3" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E3" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="I3" s="24" t="s">
-        <v>319</v>
-      </c>
-      <c r="J3" s="24" t="s">
-        <v>138</v>
       </c>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B4" s="25">
         <v>9</v>
@@ -4023,22 +4111,22 @@
         <v>5</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G4" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H4" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J4" s="32">
         <f t="shared" ref="J4:J10" si="0">SUM(B4:H4)</f>
@@ -4048,31 +4136,31 @@
     </row>
     <row r="5" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="26" t="s">
         <v>150</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>151</v>
       </c>
       <c r="D5" s="26">
         <v>2</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F5" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G5" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H5" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I5" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J5" s="26">
         <f t="shared" si="0"/>
@@ -4082,31 +4170,31 @@
     </row>
     <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D6" s="26">
         <v>5</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G6" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" s="26" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="26" t="s">
-        <v>151</v>
-      </c>
       <c r="I6" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J6" s="26">
         <f t="shared" si="0"/>
@@ -4116,31 +4204,31 @@
     </row>
     <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="26" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B7" s="26">
         <v>2</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="26">
         <v>5</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G7" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H7" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I7" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J7" s="26">
         <f t="shared" si="0"/>
@@ -4150,31 +4238,31 @@
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="26" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B8" s="26">
         <v>6</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" s="26">
         <v>4</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G8" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H8" s="26" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I8" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J8" s="26">
         <f t="shared" si="0"/>
@@ -4184,13 +4272,13 @@
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="25" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B9" s="25">
         <v>3</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" s="25">
         <v>3</v>
@@ -4199,16 +4287,16 @@
         <v>5</v>
       </c>
       <c r="F9" s="25" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="G9" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H9" s="26" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I9" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J9" s="26">
         <f t="shared" si="0"/>
@@ -4218,31 +4306,31 @@
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="32">
         <v>5</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F10" s="32">
         <v>1</v>
       </c>
       <c r="G10" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="I10" s="26" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J10" s="26">
         <f t="shared" si="0"/>
@@ -4252,19 +4340,19 @@
     </row>
     <row r="11" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="27" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B11" s="27">
         <v>2</v>
       </c>
       <c r="C11" s="27" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="27">
         <v>1</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F11" s="27">
         <v>1</v>
@@ -4286,7 +4374,7 @@
     </row>
     <row r="12" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B12" s="3">
         <f>SUM(B4:B11)</f>
@@ -4371,7 +4459,7 @@
     </row>
     <row r="2" spans="2:8" ht="27.6" x14ac:dyDescent="0.4">
       <c r="B2" s="36" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
@@ -4394,40 +4482,40 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H4" s="40"/>
     </row>
     <row r="5" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="41"/>
       <c r="C5" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="F5" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="H5" s="19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -4632,7 +4720,7 @@
     </row>
     <row r="14" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" s="15">
         <f t="shared" si="0"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC7D183-7C25-4AC3-A241-52FD330D4F61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1984C4-3CE5-4FFF-9A8A-01FE12CE70E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$69</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="397">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1534,6 +1534,22 @@
   </si>
   <si>
     <t>모돈 4두 폐사(1.22~23), 다수 식욕부진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나주 봉황면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근 2일간 모돈 2마리, 자돈 6마리 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>65번</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2257,7 +2273,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -4000,24 +4016,50 @@
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="37" t="s">
+      <c r="A68" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="B68" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="G68" s="3">
+        <v>1280</v>
+      </c>
+      <c r="H68" s="21" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B68" s="38"/>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="39"/>
-      <c r="G68" s="12">
-        <f>SUM(G3:G67)</f>
-        <v>296761</v>
-      </c>
-      <c r="H68" s="13"/>
+      <c r="B69" s="38"/>
+      <c r="C69" s="38"/>
+      <c r="D69" s="38"/>
+      <c r="E69" s="38"/>
+      <c r="F69" s="39"/>
+      <c r="G69" s="12">
+        <f>SUM(G3:G68)</f>
+        <v>298041</v>
+      </c>
+      <c r="H69" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A69:F69"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1984C4-3CE5-4FFF-9A8A-01FE12CE70E7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F497C-C909-42C5-95A8-81F34A26A66D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="396">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -467,10 +467,6 @@
   </si>
   <si>
     <t>15일과 16일 모돈 2두씩 폐사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>경기</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1809,7 +1805,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1825,9 +1821,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2288,1773 +2281,1773 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="A1" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="D2" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1280</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="G5" s="3">
+        <v>8520</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G6" s="3">
+        <v>2562</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="19" t="s">
+        <v>378</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G7" s="3">
+        <v>4050</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>302</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B3" s="23" t="s">
+      <c r="C8" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="G8" s="3">
+        <v>18586</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="G9" s="3">
+        <v>21114</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="G10" s="3">
+        <v>7945</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="19" t="s">
+        <v>374</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G11" s="3">
+        <v>2459</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="G12" s="3">
+        <v>20150</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1423</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="C14" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G14" s="3">
+        <v>847</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="28" t="s">
+        <v>370</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="G15" s="3">
+        <v>8889</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2465</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="19" t="s">
+        <v>368</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="G17" s="3">
+        <v>5983</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="G18" s="3">
+        <v>4134</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="G19" s="3">
+        <v>5232</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G20" s="3">
+        <v>4950</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2733</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="G22" s="3">
+        <v>4277</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="G23" s="3">
+        <v>4198</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F24" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1927</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="F25" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1117</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D26" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="19" t="s">
+        <v>287</v>
+      </c>
+      <c r="G26" s="3">
         <v>193</v>
       </c>
-      <c r="G3" s="5">
-        <v>2369</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="G4" s="3">
-        <v>4638</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="9" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="20" t="s">
+      <c r="H26" s="8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="G27" s="3">
+        <v>25900</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1577</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="19" t="s">
+        <v>356</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="3">
+        <v>2375</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>285</v>
+      </c>
+      <c r="G30" s="3">
+        <v>499</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="G31" s="3">
+        <v>1246</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>283</v>
+      </c>
+      <c r="G32" s="3">
+        <v>6077</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="G33" s="3">
+        <v>6118</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="B34" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="G5" s="3">
-        <v>2119</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="3">
-        <v>2273</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="20" t="s">
-        <v>322</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="G7" s="3">
-        <v>388</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="20" t="s">
-        <v>323</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="G8" s="3">
-        <v>869</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="G9" s="3">
-        <v>2</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1125</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="G11" s="3">
-        <v>2123</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="B12" s="20" t="s">
+      <c r="C34" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>281</v>
+      </c>
+      <c r="G34" s="3">
+        <v>9724</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="B35" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G12" s="3">
-        <v>2661</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="G13" s="3">
-        <v>19</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" s="3">
-        <v>2267</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2916</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="G16" s="3">
-        <v>4245</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="20" t="s">
-        <v>332</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="G17" s="3">
-        <v>726</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1020</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="20" t="s">
-        <v>334</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G19" s="3">
-        <v>385</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="20" t="s">
-        <v>335</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="G20" s="3">
-        <v>2387</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>220</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1801</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="G22" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="20" t="s">
-        <v>338</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="G23" s="3">
-        <v>579</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1175</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="20" t="s">
-        <v>340</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="G25" s="3">
-        <v>5614</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="F26" s="20" t="s">
-        <v>271</v>
-      </c>
-      <c r="G26" s="3">
-        <v>8243</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>272</v>
-      </c>
-      <c r="G27" s="3">
-        <v>6824</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D28" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="F28" s="20" t="s">
-        <v>273</v>
-      </c>
-      <c r="G28" s="3">
-        <v>5203</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>274</v>
-      </c>
-      <c r="G29" s="3">
-        <v>1133</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D30" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F30" s="20" t="s">
-        <v>275</v>
-      </c>
-      <c r="G30" s="3">
-        <v>5499</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="20" t="s">
-        <v>346</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="G31" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="F32" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>278</v>
-      </c>
-      <c r="G33" s="3">
-        <v>2009</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>279</v>
-      </c>
-      <c r="G34" s="3">
-        <v>1956</v>
-      </c>
-      <c r="H34" s="9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>251</v>
+      <c r="C35" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>250</v>
       </c>
       <c r="E35" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="F35" s="19" t="s">
         <v>280</v>
       </c>
       <c r="G35" s="3">
+        <v>10218</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A36" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>279</v>
+      </c>
+      <c r="G36" s="3">
         <v>12842</v>
       </c>
-      <c r="H35" s="9" t="s">
+      <c r="H36" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A36" s="20" t="s">
-        <v>351</v>
-      </c>
-      <c r="B36" s="8" t="s">
+    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D37" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1956</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="G36" s="3">
-        <v>10218</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="B37" s="8" t="s">
+      <c r="C38" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F38" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="G38" s="3">
+        <v>2009</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" s="19" t="s">
+        <v>276</v>
+      </c>
+      <c r="G39" s="3">
+        <v>2369</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="B40" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D37" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="F37" s="20" t="s">
-        <v>282</v>
-      </c>
-      <c r="G37" s="3">
-        <v>9724</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A38" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="B38" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C38" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="F38" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="G38" s="3">
-        <v>6118</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="B39" s="8" t="s">
+      <c r="C40" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F40" s="19" t="s">
+        <v>275</v>
+      </c>
+      <c r="G40" s="3">
+        <v>8094</v>
+      </c>
+      <c r="H40" s="19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="B41" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="F39" s="20" t="s">
-        <v>284</v>
-      </c>
-      <c r="G39" s="3">
-        <v>6077</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="B40" s="8" t="s">
+      <c r="C41" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>274</v>
+      </c>
+      <c r="G41" s="3">
+        <v>5499</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D42" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>273</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1133</v>
+      </c>
+      <c r="H42" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D43" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>272</v>
+      </c>
+      <c r="G43" s="3">
+        <v>5203</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F44" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="G44" s="3">
+        <v>6824</v>
+      </c>
+      <c r="H44" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A45" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B45" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D40" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F40" s="20" t="s">
-        <v>285</v>
-      </c>
-      <c r="G40" s="3">
-        <v>1246</v>
-      </c>
-      <c r="H40" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="20" t="s">
-        <v>356</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="G41" s="3">
-        <v>499</v>
-      </c>
-      <c r="H41" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="C42" s="20" t="s">
+      <c r="C45" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D45" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="G45" s="3">
+        <v>8243</v>
+      </c>
+      <c r="H45" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A46" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>269</v>
+      </c>
+      <c r="G46" s="3">
+        <v>5614</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A47" s="19" t="s">
+        <v>338</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D47" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="G47" s="3">
+        <v>1175</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A48" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="G48" s="3">
+        <v>579</v>
+      </c>
+      <c r="H48" s="19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="19" t="s">
+        <v>336</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F49" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="G49" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="19" t="s">
+        <v>335</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F50" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="G50" s="3">
+        <v>1801</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A51" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="F51" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="G51" s="3">
+        <v>2387</v>
+      </c>
+      <c r="H51" s="19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A52" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="C52" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>139</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>263</v>
+      </c>
+      <c r="G52" s="3">
+        <v>385</v>
+      </c>
+      <c r="H52" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A53" s="19" t="s">
+        <v>332</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F53" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="G53" s="3">
+        <v>1020</v>
+      </c>
+      <c r="H53" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A54" s="19" t="s">
+        <v>331</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="C54" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="F54" s="19" t="s">
+        <v>217</v>
+      </c>
+      <c r="G54" s="3">
+        <v>726</v>
+      </c>
+      <c r="H54" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="19" t="s">
+        <v>330</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>216</v>
+      </c>
+      <c r="G55" s="3">
+        <v>4245</v>
+      </c>
+      <c r="H55" s="19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A56" s="19" t="s">
+        <v>329</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F56" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G56" s="3">
+        <v>2916</v>
+      </c>
+      <c r="H56" s="19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A57" s="19" t="s">
+        <v>328</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2267</v>
+      </c>
+      <c r="H57" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A58" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="G42" s="3">
-        <v>2375</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="F43" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1577</v>
-      </c>
-      <c r="H43" s="20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="C44" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F44" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="G44" s="3">
-        <v>25900</v>
-      </c>
-      <c r="H44" s="20" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A45" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="C45" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="F45" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="D58" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G58" s="3">
+        <v>19</v>
+      </c>
+      <c r="H58" s="19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A59" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F59" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G59" s="3">
+        <v>2661</v>
+      </c>
+      <c r="H59" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="B60" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F60" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="G60" s="3">
+        <v>2123</v>
+      </c>
+      <c r="H60" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A61" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F61" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="G61" s="3">
+        <v>1125</v>
+      </c>
+      <c r="H61" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A62" s="19" t="s">
+        <v>323</v>
+      </c>
+      <c r="B62" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C62" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F62" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2</v>
+      </c>
+      <c r="H62" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A63" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="B63" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C63" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D63" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="G63" s="3">
+        <v>869</v>
+      </c>
+      <c r="H63" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A64" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B64" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G64" s="3">
+        <v>388</v>
+      </c>
+      <c r="H64" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A65" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B65" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F65" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2273</v>
+      </c>
+      <c r="H65" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A66" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B66" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="H45" s="20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A46" s="20" t="s">
-        <v>361</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F46" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="G46" s="3">
-        <v>1117</v>
-      </c>
-      <c r="H46" s="20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A47" s="20" t="s">
-        <v>362</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F47" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1927</v>
-      </c>
-      <c r="H47" s="20" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A48" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="B48" s="20" t="s">
+      <c r="F66" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H66" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B67" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="G48" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H48" s="20" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="B49" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C49" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D49" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="G49" s="3">
-        <v>4277</v>
-      </c>
-      <c r="H49" s="21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="G50" s="3">
-        <v>2733</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A51" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="B51" s="20" t="s">
+      <c r="C67" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G67" s="3">
+        <v>4638</v>
+      </c>
+      <c r="H67" s="19" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="B68" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C51" s="20" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="F51" s="20" t="s">
-        <v>250</v>
-      </c>
-      <c r="G51" s="3">
-        <v>4950</v>
-      </c>
-      <c r="H51" s="21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A52" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="D52" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5232</v>
-      </c>
-      <c r="H52" s="21" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="B53" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="G53" s="3">
-        <v>4134</v>
-      </c>
-      <c r="H53" s="21" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5983</v>
-      </c>
-      <c r="H54" s="21" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="C55" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F55" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="G55" s="3">
-        <v>2465</v>
-      </c>
-      <c r="H55" s="21" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="29" t="s">
-        <v>371</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="G56" s="3">
-        <v>8889</v>
-      </c>
-      <c r="H56" s="21" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="20" t="s">
-        <v>372</v>
-      </c>
-      <c r="B57" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="20" t="s">
-        <v>165</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="G57" s="3">
-        <v>847</v>
-      </c>
-      <c r="H57" s="21" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="C58" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="G58" s="3">
-        <v>1423</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="B59" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C59" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="G59" s="3">
-        <v>20150</v>
-      </c>
-      <c r="H59" s="21" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="C60" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="D60" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="G60" s="3">
-        <v>2459</v>
-      </c>
-      <c r="H60" s="21" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="C61" s="20" t="s">
-        <v>178</v>
-      </c>
-      <c r="D61" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="G61" s="3">
-        <v>7945</v>
-      </c>
-      <c r="H61" s="21" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A62" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C62" s="20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D62" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="G62" s="3">
-        <v>21114</v>
-      </c>
-      <c r="H62" s="21" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A63" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="B63" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="C63" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="D63" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="G63" s="3">
-        <v>18586</v>
-      </c>
-      <c r="H63" s="21" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A64" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="B64" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>306</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="G64" s="3">
-        <v>4050</v>
-      </c>
-      <c r="H64" s="21" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>304</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>307</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="G65" s="3">
-        <v>2562</v>
-      </c>
-      <c r="H65" s="21" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A66" s="20" t="s">
-        <v>381</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="C66" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="G66" s="3">
-        <v>8520</v>
-      </c>
-      <c r="H66" s="21" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="20" t="s">
-        <v>382</v>
-      </c>
-      <c r="B67" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C67" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="G67" s="3">
-        <v>1100</v>
-      </c>
-      <c r="H67" s="21" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="20" t="s">
-        <v>396</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="C68" s="20" t="s">
-        <v>393</v>
-      </c>
-      <c r="D68" s="20" t="s">
-        <v>171</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="G68" s="3">
-        <v>1280</v>
-      </c>
-      <c r="H68" s="21" t="s">
-        <v>395</v>
+      <c r="C68" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F68" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="G68" s="5">
+        <v>2369</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="37" t="s">
+      <c r="A69" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B69" s="38"/>
-      <c r="C69" s="38"/>
-      <c r="D69" s="38"/>
-      <c r="E69" s="38"/>
-      <c r="F69" s="39"/>
-      <c r="G69" s="12">
+      <c r="B69" s="37"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="37"/>
+      <c r="F69" s="38"/>
+      <c r="G69" s="11">
         <f>SUM(G3:G68)</f>
         <v>298041</v>
       </c>
-      <c r="H69" s="13"/>
+      <c r="H69" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4079,30 +4072,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A2" s="22"/>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="35"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="34"/>
       <c r="J2" s="2" t="e">
         <f>사육돼지!#REF!</f>
         <v>#REF!</v>
@@ -4110,305 +4103,305 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="J3" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B3" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" s="24" t="s">
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" s="24">
+        <v>9</v>
+      </c>
+      <c r="C4" s="24">
+        <v>5</v>
+      </c>
+      <c r="D4" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="H3" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="I3" s="24" t="s">
+      <c r="E4" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="F4" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="J3" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" spans="1:11" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="B4" s="25">
-        <v>9</v>
-      </c>
-      <c r="C4" s="25">
-        <v>5</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" s="25" t="s">
-        <v>317</v>
-      </c>
-      <c r="G4" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="H4" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="J4" s="32">
+      <c r="G4" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="J4" s="31">
         <f t="shared" ref="J4:J10" si="0">SUM(B4:H4)</f>
         <v>14</v>
       </c>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="B5" s="26" t="s">
+      <c r="A5" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="26">
+      <c r="D5" s="25">
         <v>2</v>
       </c>
-      <c r="E5" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="H5" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="I5" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J5" s="26">
+      <c r="E5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="G5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="I5" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J5" s="25">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="26" t="s">
+      <c r="A6" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D6" s="25">
+        <v>5</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="F6" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="D6" s="26">
-        <v>5</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G6" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="I6" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J6" s="26">
+      <c r="I6" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J6" s="25">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="26" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="26">
+      <c r="A7" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B7" s="25">
         <v>2</v>
       </c>
-      <c r="C7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D7" s="26">
+      <c r="C7" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="25">
         <v>5</v>
       </c>
-      <c r="E7" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="I7" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J7" s="26">
+      <c r="E7" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J7" s="25">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="26">
+      <c r="A8" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" s="25">
         <v>6</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="C8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="25">
         <v>4</v>
       </c>
-      <c r="E8" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>317</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="I8" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J8" s="26">
+      <c r="E8" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J8" s="25">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="B9" s="25">
+      <c r="A9" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B9" s="24">
         <v>3</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D9" s="25">
+      <c r="C9" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="D9" s="24">
         <v>3</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="24">
         <v>5</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>317</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="H9" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="I9" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J9" s="26">
+      <c r="F9" s="24" t="s">
+        <v>316</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="I9" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J9" s="25">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="B10" s="31">
+        <v>5</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="D10" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B10" s="32">
-        <v>5</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="D10" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="E10" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="31">
         <v>1</v>
       </c>
-      <c r="G10" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="H10" s="26" t="s">
-        <v>184</v>
-      </c>
-      <c r="I10" s="26" t="s">
-        <v>149</v>
-      </c>
-      <c r="J10" s="26">
+      <c r="G10" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="J10" s="25">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="27" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="27">
+      <c r="A11" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="26">
         <v>2</v>
       </c>
-      <c r="C11" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="D11" s="27">
+      <c r="C11" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="26">
         <v>1</v>
       </c>
-      <c r="E11" s="27" t="s">
-        <v>161</v>
-      </c>
-      <c r="F11" s="27">
+      <c r="E11" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="26">
         <v>1</v>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="26">
         <v>1</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="26">
         <v>1</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="26">
         <v>1</v>
       </c>
-      <c r="J11" s="31">
+      <c r="J11" s="30">
         <f>SUM(B11:I11)</f>
         <v>7</v>
       </c>
@@ -4416,7 +4409,7 @@
     </row>
     <row r="12" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" s="3">
         <f>SUM(B4:B11)</f>
@@ -4491,300 +4484,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="2:8" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
       <c r="H3" s="2" t="e">
         <f>사육돼지!#REF!</f>
         <v>#REF!</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40" t="s">
+      <c r="D4" s="39"/>
+      <c r="E4" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40" t="s">
+      <c r="F4" s="39"/>
+      <c r="G4" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="40"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="41"/>
-      <c r="C5" s="19" t="s">
+      <c r="B5" s="40"/>
+      <c r="C5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="18" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="17">
+      <c r="B6" s="16">
         <v>2019</v>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="17">
         <f t="shared" ref="C6:D14" si="0">E6+G6</f>
         <v>239</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="17">
         <f t="shared" si="0"/>
         <v>364839</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="17">
         <v>14</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="17">
         <v>28014</v>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="17">
         <v>225</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <v>336825</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>2020</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="14">
         <f t="shared" si="0"/>
         <v>4940</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="14">
         <v>2</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="14">
         <v>1746</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="14">
         <v>4</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="14">
         <v>3194</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>2021</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="14">
         <f t="shared" si="0"/>
         <v>9472</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="14">
         <v>5</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="14">
         <v>7452</v>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="14">
         <v>1</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H8" s="14">
         <v>2020</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>2022</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="14">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="14">
         <f t="shared" si="0"/>
         <v>34788</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="14">
         <v>7</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="14">
         <v>33691</v>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="14">
         <v>1</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="14">
         <v>1097</v>
       </c>
     </row>
     <row r="10" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>2023</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="14">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="D10" s="15">
+      <c r="D10" s="14">
         <f t="shared" si="0"/>
         <v>104361</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="14">
         <v>10</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="14">
         <v>60653</v>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="14">
         <v>15</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="14">
         <v>43708</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>2024</v>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="14">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="14">
         <f t="shared" si="0"/>
         <v>49746</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="14">
         <v>11</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="14">
         <v>49746</v>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <v>2025</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="14">
         <f t="shared" ref="C12:C13" si="1">E12+G12</f>
         <v>11</v>
       </c>
-      <c r="D12" s="15">
+      <c r="D12" s="14">
         <f t="shared" ref="D12:D13" si="2">F12+H12</f>
         <v>34030</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="14">
         <v>6</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="14">
         <v>28973</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="14">
         <v>5</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <v>5057</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>2026</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f t="shared" si="2"/>
         <v>75112</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <v>7</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <v>75112</v>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <v>0</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f t="shared" si="0"/>
         <v>313</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f t="shared" si="0"/>
         <v>677288</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>SUM(E6:E13)</f>
         <v>62</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f>SUM(F6:F13)</f>
         <v>285387</v>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f>SUM(G6:G13)</f>
         <v>251</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <f>SUM(H6:H13)</f>
         <v>391901</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502F497C-C909-42C5-95A8-81F34A26A66D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FBFB54-E493-42F9-BEF6-035C1FFC2C26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$70</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="401">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1546,6 +1546,26 @@
   </si>
   <si>
     <t>65번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>당진 순성면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>최근 2일간 이유자돈, 육성돈 67두 폐사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2266,7 +2286,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2320,117 +2340,117 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G3" s="3">
-        <v>1280</v>
+        <v>5223</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="8" t="s">
-        <v>381</v>
+      <c r="A4" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>384</v>
+        <v>174</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G4" s="3">
-        <v>1100</v>
+        <v>1280</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="19" t="s">
-        <v>380</v>
+      <c r="A5" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G5" s="3">
-        <v>8520</v>
+        <v>1100</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="G6" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
@@ -2439,1620 +2459,1646 @@
         <v>308</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G7" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G8" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G9" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="G10" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G11" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>391</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G12" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>179</v>
+        <v>391</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G13" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G14" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="28" t="s">
-        <v>370</v>
+      <c r="A15" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="G15" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="19" t="s">
-        <v>369</v>
+      <c r="A16" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G16" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G17" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B18" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G18" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G19" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G20" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G21" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B22" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="G22" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>290</v>
+        <v>247</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G23" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>106</v>
+        <v>4277</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G24" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G25" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G26" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="G27" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G28" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G29" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>131</v>
+        <v>356</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G30" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G31" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G32" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G33" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G34" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G35" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G36" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G37" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G38" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G39" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>91</v>
+        <v>2009</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>33</v>
+        <v>346</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G40" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>89</v>
+        <v>2369</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G41" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G42" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G43" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G44" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G45" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G46" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G47" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B48" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G48" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G49" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G50" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G51" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G52" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="G53" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G54" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G55" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G56" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>215</v>
       </c>
       <c r="G57" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G58" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F59" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G59" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G60" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G61" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G62" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B63" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G63" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G64" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G65" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G66" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G67" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H67" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A68" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C68" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F67" s="19" t="s">
+      <c r="F68" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G67" s="3">
+      <c r="G68" s="3">
         <v>4638</v>
       </c>
-      <c r="H67" s="19" t="s">
+      <c r="H68" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A68" s="22" t="s">
+    <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B68" s="22" t="s">
+      <c r="B69" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C68" s="22" t="s">
+      <c r="C69" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D68" s="33" t="s">
+      <c r="D69" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E69" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F68" s="22" t="s">
+      <c r="F69" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G68" s="5">
+      <c r="G69" s="5">
         <v>2369</v>
       </c>
-      <c r="H68" s="22" t="s">
+      <c r="H69" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="36" t="s">
+    <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B69" s="37"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="37"/>
-      <c r="F69" s="38"/>
-      <c r="G69" s="11">
-        <f>SUM(G3:G68)</f>
-        <v>298041</v>
-      </c>
-      <c r="H69" s="12"/>
+      <c r="B70" s="37"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="37"/>
+      <c r="F70" s="38"/>
+      <c r="G70" s="11">
+        <f>SUM(G3:G69)</f>
+        <v>303264</v>
+      </c>
+      <c r="H70" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A69:F69"/>
+    <mergeCell ref="A70:F70"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7FBFB54-E493-42F9-BEF6-035C1FFC2C26}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6BE966-E719-4956-9830-A11FECF5BE44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="411">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1566,6 +1566,46 @@
   </si>
   <si>
     <t>최근 2일간 이유자돈, 육성돈 67두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>67번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>68번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>69번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍성 은하면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경북 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김천 구성면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정읍 덕천면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12일 자돈 6두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12일 자돈 10두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8일 모돈 1두, 12일 모돈 2두 폐사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2286,7 +2326,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2339,661 +2379,661 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="8" t="s">
-        <v>396</v>
+      <c r="A3" s="19" t="s">
+        <v>403</v>
       </c>
       <c r="B3" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>397</v>
+      <c r="C3" s="19" t="s">
+        <v>404</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G3" s="3">
-        <v>5223</v>
+        <v>2900</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>174</v>
+        <v>405</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G4" s="3">
-        <v>1280</v>
+        <v>2759</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>394</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="8" t="s">
-        <v>381</v>
+      <c r="A5" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>384</v>
+        <v>302</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="G5" s="3">
-        <v>1100</v>
+        <v>4882</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
-        <v>380</v>
+      <c r="A6" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>382</v>
+        <v>166</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="G6" s="3">
-        <v>8520</v>
+        <v>5223</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>306</v>
+        <v>174</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>308</v>
+        <v>393</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>309</v>
+        <v>393</v>
       </c>
       <c r="G7" s="3">
-        <v>2562</v>
+        <v>1280</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>313</v>
+        <v>394</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
-        <v>378</v>
+      <c r="A8" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>308</v>
+        <v>387</v>
       </c>
       <c r="G8" s="3">
-        <v>4050</v>
+        <v>1100</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>302</v>
+        <v>382</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>304</v>
+        <v>383</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="G9" s="3">
-        <v>18586</v>
+        <v>8520</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>312</v>
+        <v>389</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>178</v>
+        <v>306</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G10" s="3">
-        <v>21114</v>
+        <v>2562</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>181</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>177</v>
+        <v>305</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>261</v>
+        <v>308</v>
       </c>
       <c r="G11" s="3">
-        <v>7945</v>
+        <v>4050</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>180</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>176</v>
+        <v>302</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>304</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>260</v>
+        <v>307</v>
       </c>
       <c r="G12" s="3">
-        <v>2459</v>
+        <v>18586</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>391</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G13" s="3">
-        <v>20150</v>
+        <v>21114</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="G14" s="3">
-        <v>1423</v>
+        <v>7945</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>164</v>
+        <v>172</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="G15" s="3">
-        <v>847</v>
+        <v>2459</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>163</v>
+        <v>391</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="28" t="s">
-        <v>370</v>
+      <c r="A16" s="19" t="s">
+        <v>373</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>14</v>
+        <v>171</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>256</v>
+        <v>310</v>
       </c>
       <c r="G16" s="3">
-        <v>8889</v>
+        <v>20150</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>295</v>
+        <v>258</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>297</v>
       </c>
       <c r="G17" s="3">
-        <v>2465</v>
+        <v>1423</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>294</v>
+        <v>257</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="G18" s="3">
-        <v>5983</v>
+        <v>847</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="19" t="s">
-        <v>367</v>
+      <c r="A19" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>153</v>
+        <v>14</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>293</v>
+        <v>256</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G19" s="3">
-        <v>4134</v>
+        <v>8889</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="G20" s="3">
-        <v>5232</v>
+        <v>2465</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>249</v>
+        <v>294</v>
       </c>
       <c r="G21" s="3">
-        <v>4950</v>
+        <v>5983</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G22" s="3">
-        <v>2733</v>
+        <v>4134</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>110</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>247</v>
+        <v>292</v>
       </c>
       <c r="G23" s="3">
-        <v>4277</v>
+        <v>5232</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F24" s="19" t="s">
-        <v>290</v>
+        <v>249</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="G24" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>106</v>
+        <v>4950</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>289</v>
+        <v>248</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="G25" s="3">
-        <v>1927</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>104</v>
+        <v>2733</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>288</v>
+        <v>247</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G26" s="3">
-        <v>1117</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>103</v>
+        <v>4277</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G27" s="3">
-        <v>193</v>
+        <v>4198</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>98</v>
@@ -3002,1103 +3042,1181 @@
         <v>87</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>236</v>
+        <v>289</v>
       </c>
       <c r="G28" s="3">
-        <v>25900</v>
+        <v>1927</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>235</v>
+        <v>288</v>
       </c>
       <c r="G29" s="3">
-        <v>1577</v>
+        <v>1117</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>15</v>
+        <v>99</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="F30" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G30" s="3">
-        <v>2375</v>
+        <v>193</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>131</v>
+        <v>358</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>132</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="G31" s="3">
-        <v>499</v>
+        <v>25900</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>124</v>
+        <v>357</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>120</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>284</v>
+        <v>235</v>
       </c>
       <c r="G32" s="3">
-        <v>1246</v>
+        <v>1577</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>122</v>
+        <v>356</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G33" s="3">
-        <v>6077</v>
+        <v>2375</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G34" s="3">
-        <v>6118</v>
+        <v>499</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="G35" s="3">
-        <v>9724</v>
+        <v>1246</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G36" s="3">
-        <v>10218</v>
+        <v>6077</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="G37" s="3">
-        <v>12842</v>
+        <v>6118</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G38" s="3">
-        <v>1956</v>
+        <v>9724</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="G39" s="3">
-        <v>2009</v>
+        <v>10218</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="G40" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>91</v>
+        <v>12842</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C41" s="19" t="s">
-        <v>33</v>
+        <v>348</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G41" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>89</v>
+        <v>1956</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>32</v>
+        <v>347</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="G42" s="3">
-        <v>5499</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>63</v>
+        <v>2009</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>343</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C43" s="19" t="s">
-        <v>31</v>
+        <v>346</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G43" s="3">
-        <v>1133</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>62</v>
+        <v>2369</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G44" s="3">
-        <v>5203</v>
+        <v>8094</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G45" s="3">
-        <v>6824</v>
+        <v>5499</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B46" s="19" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="G46" s="3">
-        <v>8243</v>
+        <v>1133</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B47" s="19" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="G47" s="3">
-        <v>5614</v>
+        <v>5203</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B48" s="19" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="G48" s="3">
-        <v>1175</v>
+        <v>6824</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="G49" s="3">
-        <v>579</v>
+        <v>8243</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="G50" s="3">
-        <v>2300</v>
+        <v>5614</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="G51" s="3">
-        <v>1801</v>
+        <v>1175</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G52" s="3">
-        <v>2387</v>
+        <v>579</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="G53" s="3">
-        <v>385</v>
+        <v>2300</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>218</v>
+        <v>265</v>
       </c>
       <c r="G54" s="3">
-        <v>1020</v>
+        <v>1801</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>217</v>
+        <v>264</v>
       </c>
       <c r="G55" s="3">
-        <v>726</v>
+        <v>2387</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>216</v>
+        <v>263</v>
       </c>
       <c r="G56" s="3">
-        <v>4245</v>
+        <v>385</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G57" s="3">
-        <v>2916</v>
+        <v>1020</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G58" s="3">
-        <v>2267</v>
+        <v>726</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="G59" s="3">
-        <v>19</v>
+        <v>4245</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G60" s="3">
-        <v>2661</v>
+        <v>2916</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G61" s="3">
-        <v>2123</v>
+        <v>2267</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="G62" s="3">
-        <v>1125</v>
+        <v>19</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>212</v>
+        <v>189</v>
       </c>
       <c r="G63" s="3">
-        <v>2</v>
+        <v>2661</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>88</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G64" s="3">
-        <v>869</v>
+        <v>2123</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B65" s="19" t="s">
         <v>114</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G65" s="3">
-        <v>388</v>
+        <v>1125</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G66" s="3">
-        <v>2273</v>
+        <v>2</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G67" s="3">
-        <v>2119</v>
+        <v>869</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G68" s="3">
+        <v>388</v>
+      </c>
+      <c r="H68" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A69" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B69" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C69" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F69" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G69" s="3">
+        <v>2273</v>
+      </c>
+      <c r="H69" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A70" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B70" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F70" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H70" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A71" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B71" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C71" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E71" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F68" s="19" t="s">
+      <c r="F71" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G71" s="3">
         <v>4638</v>
       </c>
-      <c r="H68" s="19" t="s">
+      <c r="H71" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A69" s="22" t="s">
+    <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B69" s="22" t="s">
+      <c r="B72" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C69" s="22" t="s">
+      <c r="C72" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D69" s="33" t="s">
+      <c r="D72" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E72" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F69" s="22" t="s">
+      <c r="F72" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G69" s="5">
+      <c r="G72" s="5">
         <v>2369</v>
       </c>
-      <c r="H69" s="22" t="s">
+      <c r="H72" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A70" s="36" t="s">
+    <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B70" s="37"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="37"/>
-      <c r="F70" s="38"/>
-      <c r="G70" s="11">
-        <f>SUM(G3:G69)</f>
+      <c r="B73" s="37"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="37"/>
+      <c r="F73" s="38"/>
+      <c r="G73" s="11">
+        <f>SUM(G6:G72)</f>
         <v>303264</v>
       </c>
-      <c r="H70" s="12"/>
+      <c r="H73" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A73:F73"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6BE966-E719-4956-9830-A11FECF5BE44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C85B47-CB22-4E40-9B8D-734994F28B89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="432">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1606,6 +1606,90 @@
   </si>
   <si>
     <t>8일 모돈 1두, 12일 모돈 2두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>72번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>73번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>74번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경남</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창녕 창녕읍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철원 갈말읍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철원 서면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화성 장안면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>평택 오성면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13일 환경시료 양성, 14일 자돈 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자돈 12두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모돈 1두, 포유자돈 35두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전국 양돈농장 환경검사 양성 (재검사 진행)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2326,7 +2410,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2380,1843 +2464,1973 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>166</v>
+        <v>422</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="G3" s="3">
-        <v>2900</v>
+        <v>2537</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>405</v>
+        <v>422</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="G4" s="3">
-        <v>2759</v>
+        <v>4500</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>302</v>
+        <v>425</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="G5" s="3">
-        <v>4882</v>
+        <v>830</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="8" t="s">
-        <v>396</v>
+      <c r="A6" s="19" t="s">
+        <v>412</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>397</v>
+        <v>425</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>426</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="G6" s="3">
-        <v>5223</v>
+        <v>3400</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>400</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>174</v>
+        <v>416</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>392</v>
+        <v>417</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="G7" s="3">
-        <v>1280</v>
+        <v>1951</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>394</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="8" t="s">
-        <v>381</v>
+      <c r="A8" s="19" t="s">
+        <v>403</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>384</v>
+        <v>166</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>404</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="G8" s="3">
-        <v>1100</v>
+        <v>2900</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>383</v>
+        <v>405</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>406</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="G9" s="3">
-        <v>8520</v>
+        <v>2759</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>306</v>
+        <v>302</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>309</v>
+        <v>399</v>
       </c>
       <c r="G10" s="3">
-        <v>2562</v>
+        <v>4882</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>313</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="19" t="s">
-        <v>378</v>
+      <c r="A11" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>166</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>308</v>
+        <v>398</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>308</v>
+        <v>399</v>
       </c>
       <c r="G11" s="3">
-        <v>4050</v>
+        <v>5223</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>302</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>304</v>
+        <v>174</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>307</v>
+        <v>393</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>307</v>
+        <v>393</v>
       </c>
       <c r="G12" s="3">
-        <v>18586</v>
+        <v>1280</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>312</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="19" t="s">
-        <v>376</v>
+      <c r="A13" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>178</v>
+        <v>384</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>262</v>
+        <v>386</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>311</v>
+        <v>387</v>
       </c>
       <c r="G13" s="3">
-        <v>21114</v>
+        <v>1100</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>181</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>173</v>
+        <v>382</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>177</v>
+        <v>383</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>261</v>
+        <v>385</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>261</v>
+        <v>386</v>
       </c>
       <c r="G14" s="3">
-        <v>7945</v>
+        <v>8520</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>180</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>176</v>
+        <v>303</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>306</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>260</v>
+        <v>308</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>260</v>
+        <v>309</v>
       </c>
       <c r="G15" s="3">
-        <v>2459</v>
+        <v>2562</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>391</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>175</v>
+        <v>166</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>305</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="G16" s="3">
-        <v>20150</v>
+        <v>4050</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>179</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>166</v>
+        <v>302</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>167</v>
+        <v>304</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="G17" s="3">
-        <v>1423</v>
+        <v>18586</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>168</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="G18" s="3">
-        <v>847</v>
+        <v>21114</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="28" t="s">
-        <v>370</v>
+      <c r="A19" s="19" t="s">
+        <v>375</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>112</v>
+        <v>173</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="G19" s="3">
-        <v>8889</v>
+        <v>7945</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>162</v>
+        <v>172</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>295</v>
+        <v>260</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>260</v>
       </c>
       <c r="G20" s="3">
-        <v>2465</v>
+        <v>2459</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>163</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>155</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>152</v>
+        <v>171</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>294</v>
+        <v>259</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>310</v>
       </c>
       <c r="G21" s="3">
-        <v>5983</v>
+        <v>20150</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>293</v>
+        <v>258</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>297</v>
       </c>
       <c r="G22" s="3">
-        <v>4134</v>
+        <v>1423</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>292</v>
+        <v>257</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="G23" s="3">
-        <v>5232</v>
+        <v>847</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="19" t="s">
-        <v>365</v>
+      <c r="A24" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>151</v>
+        <v>14</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>249</v>
+        <v>256</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G24" s="3">
-        <v>4950</v>
+        <v>8889</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="G25" s="3">
-        <v>2733</v>
+        <v>2465</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>119</v>
+        <v>155</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="G26" s="3">
-        <v>4277</v>
+        <v>5983</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>108</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>105</v>
+        <v>153</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>290</v>
+        <v>253</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>293</v>
       </c>
       <c r="G27" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>106</v>
+        <v>4134</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>289</v>
+        <v>252</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>292</v>
       </c>
       <c r="G28" s="3">
-        <v>1927</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>104</v>
+        <v>5232</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>100</v>
+        <v>151</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>288</v>
+        <v>249</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>249</v>
       </c>
       <c r="G29" s="3">
-        <v>1117</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>103</v>
+        <v>4950</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>287</v>
+        <v>248</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="G30" s="3">
-        <v>193</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>102</v>
+        <v>2733</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>236</v>
+        <v>247</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G31" s="3">
-        <v>25900</v>
-      </c>
-      <c r="H31" s="8" t="s">
-        <v>101</v>
+        <v>4277</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F32" s="19" t="s">
-        <v>235</v>
+        <v>290</v>
       </c>
       <c r="G32" s="3">
-        <v>1577</v>
+        <v>4198</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="G33" s="3">
-        <v>2375</v>
+        <v>1927</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>131</v>
+        <v>360</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>133</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="G34" s="3">
-        <v>499</v>
+        <v>1117</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>124</v>
+        <v>359</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>131</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G35" s="3">
-        <v>1246</v>
+        <v>193</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>122</v>
+        <v>358</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>132</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="G36" s="3">
-        <v>6077</v>
+        <v>25900</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>130</v>
+        <v>357</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>120</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="G37" s="3">
-        <v>6118</v>
+        <v>1577</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>351</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>112</v>
+        <v>356</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="G38" s="3">
-        <v>9724</v>
+        <v>2375</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G39" s="3">
-        <v>10218</v>
+        <v>499</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G40" s="3">
-        <v>12842</v>
+        <v>1246</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G41" s="3">
-        <v>1956</v>
+        <v>6077</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G42" s="3">
-        <v>2009</v>
+        <v>6118</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="G43" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>91</v>
+        <v>9724</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B44" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="B44" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="19" t="s">
-        <v>33</v>
+      <c r="C44" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G44" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>89</v>
+        <v>10218</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C45" s="19" t="s">
-        <v>32</v>
+        <v>349</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>68</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G45" s="3">
-        <v>5499</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>63</v>
+        <v>12842</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>343</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="C46" s="19" t="s">
-        <v>31</v>
+        <v>348</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G46" s="3">
-        <v>1133</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>62</v>
+        <v>1956</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C47" s="19" t="s">
-        <v>30</v>
+        <v>347</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G47" s="3">
-        <v>5203</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>61</v>
+        <v>2009</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>341</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>29</v>
+        <v>346</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="G48" s="3">
-        <v>6824</v>
-      </c>
-      <c r="H48" s="19" t="s">
-        <v>48</v>
+        <v>2369</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G49" s="3">
-        <v>8243</v>
+        <v>8094</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G50" s="3">
-        <v>5614</v>
+        <v>5499</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G51" s="3">
-        <v>1175</v>
+        <v>1133</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G52" s="3">
-        <v>579</v>
+        <v>5203</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G53" s="3">
-        <v>2300</v>
+        <v>6824</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G54" s="3">
-        <v>1801</v>
+        <v>8243</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>204</v>
+        <v>223</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G55" s="3">
-        <v>2387</v>
+        <v>5614</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G56" s="3">
-        <v>385</v>
+        <v>1175</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="G57" s="3">
-        <v>1020</v>
+        <v>579</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>220</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>217</v>
+        <v>266</v>
       </c>
       <c r="G58" s="3">
-        <v>726</v>
+        <v>2300</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>200</v>
+        <v>219</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>216</v>
+        <v>265</v>
       </c>
       <c r="G59" s="3">
-        <v>4245</v>
+        <v>1801</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>215</v>
+        <v>264</v>
       </c>
       <c r="G60" s="3">
-        <v>2916</v>
+        <v>2387</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>37</v>
+        <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>215</v>
+        <v>263</v>
       </c>
       <c r="G61" s="3">
-        <v>2267</v>
+        <v>385</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>189</v>
+        <v>218</v>
       </c>
       <c r="G62" s="3">
-        <v>19</v>
+        <v>1020</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="G63" s="3">
-        <v>2661</v>
+        <v>726</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G64" s="3">
-        <v>2123</v>
+        <v>4245</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G65" s="3">
-        <v>1125</v>
+        <v>2916</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G66" s="3">
-        <v>2</v>
+        <v>2267</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="G67" s="3">
-        <v>869</v>
+        <v>19</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="G68" s="3">
-        <v>388</v>
+        <v>2661</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="G69" s="3">
-        <v>2273</v>
+        <v>2123</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="G70" s="3">
-        <v>2119</v>
+        <v>1125</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="G71" s="3">
+        <v>2</v>
+      </c>
+      <c r="H71" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A72" s="19" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="C72" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="F72" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="G72" s="3">
+        <v>869</v>
+      </c>
+      <c r="H72" s="19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A73" s="19" t="s">
+        <v>321</v>
+      </c>
+      <c r="B73" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F73" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="G73" s="3">
+        <v>388</v>
+      </c>
+      <c r="H73" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B74" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F74" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2273</v>
+      </c>
+      <c r="H74" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A75" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C75" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F75" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G75" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H75" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A76" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E76" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F71" s="19" t="s">
+      <c r="F76" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G76" s="3">
         <v>4638</v>
       </c>
-      <c r="H71" s="19" t="s">
+      <c r="H76" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A72" s="22" t="s">
+    <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B72" s="22" t="s">
+      <c r="B77" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C77" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D72" s="33" t="s">
+      <c r="D77" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E77" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F72" s="22" t="s">
+      <c r="F77" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G72" s="5">
+      <c r="G77" s="5">
         <v>2369</v>
       </c>
-      <c r="H72" s="22" t="s">
+      <c r="H77" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="36" t="s">
+    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B73" s="37"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="37"/>
-      <c r="F73" s="38"/>
-      <c r="G73" s="11">
-        <f>SUM(G6:G72)</f>
-        <v>303264</v>
-      </c>
-      <c r="H73" s="12"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="11">
+        <f>SUM(G3:G77)</f>
+        <v>327023</v>
+      </c>
+      <c r="H78" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="A78:F78"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C85B47-CB22-4E40-9B8D-734994F28B89}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB15924-66E4-474D-8123-3F88A549CBA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="437">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1625,10 +1625,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>74번</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>경남</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1690,6 +1686,30 @@
   </si>
   <si>
     <t>전국 양돈농장 환경검사 양성 (재검사 진행)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전국 양돈농장 환경검사 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검사중</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>재검사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무안 함경면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산청 단성면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자돈 폐사로 인한 접수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2410,7 +2430,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2464,25 +2484,25 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>422</v>
+        <v>303</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G3" s="3">
-        <v>2537</v>
+        <v>5000</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>431</v>
@@ -2490,51 +2510,51 @@
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>422</v>
+        <v>174</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="G4" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G5" s="3">
-        <v>830</v>
+        <v>2537</v>
       </c>
       <c r="H5" s="20" t="s">
         <v>430</v>
@@ -2542,117 +2562,117 @@
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G6" s="3">
-        <v>3400</v>
+        <v>4500</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G7" s="3">
-        <v>1951</v>
+        <v>830</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>166</v>
+        <v>424</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="G8" s="3">
-        <v>2900</v>
+        <v>3400</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G9" s="3">
-        <v>2759</v>
+        <v>1951</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
@@ -2664,460 +2684,460 @@
         <v>399</v>
       </c>
       <c r="G10" s="3">
-        <v>4882</v>
+        <v>2900</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
-        <v>396</v>
+      <c r="A11" s="19" t="s">
+        <v>402</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>397</v>
+        <v>405</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>406</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G11" s="3">
-        <v>5223</v>
+        <v>2759</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G12" s="3">
-        <v>1280</v>
+        <v>4882</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="G13" s="3">
-        <v>1100</v>
+        <v>5223</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>383</v>
+        <v>174</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="G14" s="3">
-        <v>8520</v>
+        <v>1280</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="19" t="s">
-        <v>379</v>
+      <c r="A15" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>306</v>
+        <v>384</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>309</v>
+        <v>387</v>
       </c>
       <c r="G15" s="3">
-        <v>2562</v>
+        <v>1100</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>166</v>
+        <v>382</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="G16" s="3">
-        <v>4050</v>
+        <v>8520</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G17" s="3">
-        <v>18586</v>
+        <v>2562</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>178</v>
+        <v>305</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G18" s="3">
-        <v>21114</v>
+        <v>4050</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>177</v>
+        <v>304</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="G19" s="3">
-        <v>7945</v>
+        <v>18586</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>180</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="G20" s="3">
-        <v>2459</v>
+        <v>21114</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>391</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="G21" s="3">
-        <v>20150</v>
+        <v>7945</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="G22" s="3">
-        <v>1423</v>
+        <v>2459</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>168</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>164</v>
+        <v>171</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="G23" s="3">
-        <v>847</v>
+        <v>20150</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="28" t="s">
-        <v>370</v>
+      <c r="A24" s="19" t="s">
+        <v>372</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G24" s="3">
-        <v>8889</v>
+        <v>1423</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>295</v>
+        <v>257</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="G25" s="3">
-        <v>2465</v>
+        <v>847</v>
       </c>
       <c r="H25" s="20" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="19" t="s">
-        <v>368</v>
+      <c r="A26" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>294</v>
+        <v>256</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G26" s="3">
-        <v>5983</v>
+        <v>8889</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G27" s="3">
-        <v>4134</v>
+        <v>2465</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>152</v>
@@ -3126,414 +3146,414 @@
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G28" s="3">
-        <v>5232</v>
+        <v>5983</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="G29" s="3">
-        <v>4950</v>
+        <v>4134</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G30" s="3">
-        <v>2733</v>
+        <v>5232</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G31" s="3">
-        <v>4277</v>
+        <v>4950</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>290</v>
+        <v>248</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="G32" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>106</v>
+        <v>2733</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>289</v>
+        <v>247</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G33" s="3">
-        <v>1927</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>104</v>
+        <v>4277</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G34" s="3">
-        <v>1117</v>
+        <v>4198</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G35" s="3">
-        <v>193</v>
+        <v>1927</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="G36" s="3">
-        <v>25900</v>
+        <v>1117</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="G37" s="3">
-        <v>1577</v>
+        <v>193</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="G38" s="3">
-        <v>2375</v>
+        <v>25900</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>131</v>
+        <v>357</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>120</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="G39" s="3">
-        <v>499</v>
+        <v>1577</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>124</v>
+        <v>356</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G40" s="3">
-        <v>1246</v>
+        <v>2375</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G41" s="3">
-        <v>6077</v>
+        <v>499</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G42" s="3">
-        <v>6118</v>
+        <v>1246</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G43" s="3">
-        <v>9724</v>
+        <v>6077</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>69</v>
@@ -3542,895 +3562,947 @@
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G44" s="3">
-        <v>10218</v>
+        <v>6118</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G45" s="3">
-        <v>12842</v>
+        <v>9724</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G46" s="3">
-        <v>1956</v>
+        <v>10218</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G47" s="3">
-        <v>2009</v>
+        <v>12842</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>34</v>
+        <v>129</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G48" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>91</v>
+        <v>1956</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B49" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C49" s="19" t="s">
-        <v>33</v>
+      <c r="C49" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G49" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>89</v>
+        <v>2009</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B50" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B50" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="19" t="s">
-        <v>32</v>
+      <c r="C50" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G50" s="3">
-        <v>5499</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>63</v>
+        <v>2369</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G51" s="3">
-        <v>1133</v>
+        <v>8094</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G52" s="3">
-        <v>5203</v>
+        <v>5499</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G53" s="3">
-        <v>6824</v>
+        <v>1133</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G54" s="3">
-        <v>8243</v>
+        <v>5203</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G55" s="3">
-        <v>5614</v>
+        <v>6824</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G56" s="3">
-        <v>1175</v>
+        <v>8243</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G57" s="3">
-        <v>579</v>
+        <v>5614</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G58" s="3">
-        <v>2300</v>
+        <v>1175</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G59" s="3">
-        <v>1801</v>
+        <v>579</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G60" s="3">
-        <v>2387</v>
+        <v>2300</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G61" s="3">
-        <v>385</v>
+        <v>1801</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="G62" s="3">
-        <v>1020</v>
+        <v>2387</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="G63" s="3">
-        <v>726</v>
+        <v>385</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G64" s="3">
-        <v>4245</v>
+        <v>1020</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G65" s="3">
-        <v>2916</v>
+        <v>726</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G66" s="3">
-        <v>2267</v>
+        <v>4245</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G67" s="3">
-        <v>19</v>
+        <v>2916</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G68" s="3">
-        <v>2661</v>
+        <v>2267</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G69" s="3">
-        <v>2123</v>
+        <v>19</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="G70" s="3">
-        <v>1125</v>
+        <v>2661</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G71" s="3">
-        <v>2</v>
+        <v>2123</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G72" s="3">
-        <v>869</v>
+        <v>1125</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G73" s="3">
-        <v>388</v>
+        <v>2</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G74" s="3">
-        <v>2273</v>
+        <v>869</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G75" s="3">
-        <v>2119</v>
+        <v>388</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2273</v>
+      </c>
+      <c r="H76" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H77" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F76" s="19" t="s">
+      <c r="F78" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G78" s="3">
         <v>4638</v>
       </c>
-      <c r="H76" s="19" t="s">
+      <c r="H78" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="22" t="s">
+    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B79" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="22" t="s">
+      <c r="C79" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D79" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F77" s="22" t="s">
+      <c r="F79" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G79" s="5">
         <v>2369</v>
       </c>
-      <c r="H77" s="22" t="s">
+      <c r="H79" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="36" t="s">
+    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="11">
-        <f>SUM(G3:G77)</f>
-        <v>327023</v>
-      </c>
-      <c r="H78" s="12"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="11">
+        <f>SUM(G3:G79)</f>
+        <v>335523</v>
+      </c>
+      <c r="H80" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A80:F80"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB15924-66E4-474D-8123-3F88A549CBA9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C64770-D2CE-4C3B-99F3-0D9528A1214F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="433">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1653,10 +1653,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>철원 갈말읍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>철원 서면</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1685,31 +1681,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전국 양돈농장 환경검사 양성 (재검사 진행)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전국 양돈농장 환경검사 양성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>검사중</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>재검사</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>무안 함경면</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>산청 단성면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>자돈 폐사로 인한 접수</t>
+    <t>74번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자돈(35~42일령) 폐사 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>농장 일제검사(폐사체) 양성</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2430,7 +2414,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2484,13 +2468,13 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>303</v>
+        <v>174</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
@@ -2502,7 +2486,7 @@
         <v>420</v>
       </c>
       <c r="G3" s="3">
-        <v>5000</v>
+        <v>3500</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>431</v>
@@ -2510,39 +2494,39 @@
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>174</v>
+        <v>421</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>420</v>
       </c>
       <c r="G4" s="3">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
@@ -2551,24 +2535,24 @@
         <v>417</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G5" s="3">
-        <v>2537</v>
+        <v>903</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
@@ -2577,102 +2561,102 @@
         <v>417</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="G6" s="3">
-        <v>4500</v>
+        <v>3785</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G7" s="3">
-        <v>830</v>
+        <v>1951</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>424</v>
+        <v>166</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>417</v>
+        <v>399</v>
       </c>
       <c r="G8" s="3">
-        <v>3400</v>
+        <v>2962</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G9" s="3">
-        <v>1951</v>
+        <v>2722</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>427</v>
+        <v>409</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>166</v>
+        <v>302</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
@@ -2684,460 +2668,460 @@
         <v>399</v>
       </c>
       <c r="G10" s="3">
-        <v>2900</v>
+        <v>4452</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="19" t="s">
-        <v>402</v>
+      <c r="A11" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>406</v>
+        <v>166</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G11" s="3">
-        <v>2759</v>
+        <v>5223</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>302</v>
+        <v>174</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="G12" s="3">
-        <v>4882</v>
+        <v>1458</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="G13" s="3">
-        <v>5223</v>
+        <v>1194</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>392</v>
+        <v>382</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>383</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="G14" s="3">
-        <v>1280</v>
+        <v>8520</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>381</v>
+      <c r="A15" s="19" t="s">
+        <v>379</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>112</v>
+        <v>303</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>384</v>
+        <v>306</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>387</v>
+        <v>309</v>
       </c>
       <c r="G15" s="3">
-        <v>1100</v>
+        <v>2562</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>388</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>382</v>
+        <v>166</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>383</v>
+        <v>305</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>385</v>
+        <v>308</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>386</v>
+        <v>308</v>
       </c>
       <c r="G16" s="3">
-        <v>8520</v>
+        <v>4050</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G17" s="3">
-        <v>2562</v>
+        <v>18586</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>305</v>
+        <v>178</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>308</v>
+        <v>262</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G18" s="3">
-        <v>4050</v>
+        <v>21114</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>390</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>302</v>
+        <v>173</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>304</v>
+        <v>177</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>307</v>
+        <v>261</v>
       </c>
       <c r="G19" s="3">
-        <v>18586</v>
+        <v>7945</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>312</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>178</v>
+        <v>172</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>311</v>
+        <v>260</v>
       </c>
       <c r="G20" s="3">
-        <v>21114</v>
+        <v>2459</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>181</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>177</v>
+        <v>171</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>261</v>
+        <v>310</v>
       </c>
       <c r="G21" s="3">
-        <v>7945</v>
+        <v>20150</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>176</v>
+        <v>166</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>167</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="G22" s="3">
-        <v>2459</v>
+        <v>1423</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>391</v>
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>175</v>
+        <v>112</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>164</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>170</v>
+        <v>251</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="G23" s="3">
-        <v>20150</v>
+        <v>847</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="19" t="s">
-        <v>372</v>
+      <c r="A24" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>167</v>
+        <v>14</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="G24" s="3">
-        <v>1423</v>
+        <v>8889</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>296</v>
+        <v>255</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>295</v>
       </c>
       <c r="G25" s="3">
-        <v>847</v>
+        <v>2465</v>
       </c>
       <c r="H25" s="20" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
-        <v>370</v>
+      <c r="A26" s="19" t="s">
+        <v>368</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>294</v>
       </c>
       <c r="G26" s="3">
-        <v>8889</v>
+        <v>5983</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G27" s="3">
-        <v>2465</v>
+        <v>4134</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>152</v>
@@ -3146,414 +3130,414 @@
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G28" s="3">
-        <v>5983</v>
+        <v>5232</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>251</v>
+        <v>87</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="G29" s="3">
-        <v>4134</v>
+        <v>4950</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>251</v>
+        <v>87</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G30" s="3">
-        <v>5232</v>
+        <v>2733</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G31" s="3">
-        <v>4950</v>
+        <v>4277</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>291</v>
+        <v>246</v>
+      </c>
+      <c r="F32" s="19" t="s">
+        <v>290</v>
       </c>
       <c r="G32" s="3">
-        <v>2733</v>
-      </c>
-      <c r="H32" s="20" t="s">
-        <v>110</v>
+        <v>4198</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>247</v>
+        <v>245</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>289</v>
       </c>
       <c r="G33" s="3">
-        <v>4277</v>
-      </c>
-      <c r="H33" s="20" t="s">
-        <v>108</v>
+        <v>1927</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G34" s="3">
-        <v>4198</v>
+        <v>1117</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G35" s="3">
-        <v>1927</v>
+        <v>193</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
       <c r="G36" s="3">
-        <v>1117</v>
+        <v>25900</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="G37" s="3">
-        <v>193</v>
+        <v>1577</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>236</v>
+        <v>286</v>
       </c>
       <c r="G38" s="3">
-        <v>25900</v>
+        <v>2375</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>357</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>120</v>
+        <v>355</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>235</v>
+        <v>285</v>
       </c>
       <c r="G39" s="3">
-        <v>1577</v>
+        <v>499</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>127</v>
+        <v>354</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G40" s="3">
-        <v>2375</v>
+        <v>1246</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>87</v>
+        <v>250</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G41" s="3">
-        <v>499</v>
+        <v>6077</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G42" s="3">
-        <v>1246</v>
+        <v>6118</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G43" s="3">
-        <v>6077</v>
+        <v>9724</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="C44" s="8" t="s">
         <v>69</v>
@@ -3562,947 +3546,895 @@
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G44" s="3">
-        <v>6118</v>
+        <v>10218</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G45" s="3">
-        <v>9724</v>
+        <v>12842</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G46" s="3">
-        <v>10218</v>
+        <v>1956</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G47" s="3">
-        <v>12842</v>
+        <v>2009</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>66</v>
+        <v>123</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G48" s="3">
-        <v>1956</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>67</v>
+        <v>2369</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="B49" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B49" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>35</v>
+      <c r="C49" s="19" t="s">
+        <v>33</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G49" s="3">
-        <v>2009</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>64</v>
+        <v>8094</v>
+      </c>
+      <c r="H49" s="19" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="B50" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="B50" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>34</v>
+      <c r="C50" s="19" t="s">
+        <v>32</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G50" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>91</v>
+        <v>5499</v>
+      </c>
+      <c r="H50" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>250</v>
+        <v>38</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G51" s="3">
-        <v>8094</v>
+        <v>1133</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G52" s="3">
-        <v>5499</v>
+        <v>5203</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G53" s="3">
-        <v>1133</v>
+        <v>6824</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G54" s="3">
-        <v>5203</v>
+        <v>8243</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G55" s="3">
-        <v>6824</v>
+        <v>5614</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G56" s="3">
-        <v>8243</v>
+        <v>1175</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G57" s="3">
-        <v>5614</v>
+        <v>579</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G58" s="3">
-        <v>1175</v>
+        <v>2300</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G59" s="3">
-        <v>579</v>
+        <v>1801</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G60" s="3">
-        <v>2300</v>
+        <v>2387</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G61" s="3">
-        <v>1801</v>
+        <v>385</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>43</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B62" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>264</v>
+        <v>218</v>
       </c>
       <c r="G62" s="3">
-        <v>2387</v>
+        <v>1020</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>139</v>
+        <v>36</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>263</v>
+        <v>217</v>
       </c>
       <c r="G63" s="3">
-        <v>385</v>
+        <v>726</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G64" s="3">
-        <v>1020</v>
+        <v>4245</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G65" s="3">
-        <v>726</v>
+        <v>2916</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G66" s="3">
-        <v>4245</v>
+        <v>2267</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
       <c r="G67" s="3">
-        <v>2916</v>
+        <v>19</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B68" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="F68" s="19" t="s">
-        <v>215</v>
-      </c>
       <c r="G68" s="3">
-        <v>2267</v>
+        <v>2661</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="G69" s="3">
-        <v>19</v>
+        <v>2123</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="G70" s="3">
-        <v>2661</v>
+        <v>1125</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B71" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G71" s="3">
-        <v>2123</v>
+        <v>2</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G72" s="3">
-        <v>1125</v>
+        <v>869</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G73" s="3">
-        <v>2</v>
+        <v>388</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G74" s="3">
-        <v>869</v>
+        <v>2273</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G75" s="3">
-        <v>388</v>
+        <v>2119</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G76" s="3">
-        <v>2273</v>
+        <v>4638</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>50</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="19" t="s">
-        <v>319</v>
-      </c>
-      <c r="B77" s="19" t="s">
+      <c r="A77" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="B77" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="19" t="s">
+      <c r="C77" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="F77" s="19" t="s">
-        <v>208</v>
-      </c>
-      <c r="G77" s="3">
-        <v>2119</v>
-      </c>
-      <c r="H77" s="19" t="s">
-        <v>49</v>
+      <c r="E77" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F77" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="G77" s="5">
+        <v>2369</v>
+      </c>
+      <c r="H77" s="22" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="19" t="s">
-        <v>318</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C78" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F78" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="G78" s="3">
-        <v>4638</v>
-      </c>
-      <c r="H78" s="19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="22" t="s">
-        <v>317</v>
-      </c>
-      <c r="B79" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="C79" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D79" s="33" t="s">
-        <v>37</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F79" s="22" t="s">
-        <v>192</v>
-      </c>
-      <c r="G79" s="5">
-        <v>2369</v>
-      </c>
-      <c r="H79" s="22" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="36" t="s">
+      <c r="A78" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="11">
-        <f>SUM(G3:G79)</f>
-        <v>335523</v>
-      </c>
-      <c r="H80" s="12"/>
+      <c r="B78" s="37"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="37"/>
+      <c r="F78" s="38"/>
+      <c r="G78" s="11">
+        <f>SUM(G3:G77)</f>
+        <v>328311</v>
+      </c>
+      <c r="H78" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A78:F78"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C64770-D2CE-4C3B-99F3-0D9528A1214F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098E48BA-B2DB-4A6B-933B-C02D9A173B5A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="437">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1694,6 +1694,22 @@
   </si>
   <si>
     <t>농장 일제검사(폐사체) 양성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의령 부림면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자돈(50~60일령) 폐사 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2414,7 +2430,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H78"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2468,65 +2484,65 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G3" s="3">
-        <v>3500</v>
+        <v>10643</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>421</v>
+        <v>174</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>420</v>
       </c>
       <c r="G4" s="3">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
@@ -2535,24 +2551,24 @@
         <v>417</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G5" s="3">
-        <v>903</v>
+        <v>4500</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>423</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
@@ -2564,73 +2580,73 @@
         <v>417</v>
       </c>
       <c r="G6" s="3">
-        <v>3785</v>
+        <v>903</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G7" s="3">
-        <v>1951</v>
+        <v>3785</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G8" s="3">
-        <v>2962</v>
+        <v>1951</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>405</v>
+        <v>166</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
@@ -2642,21 +2658,21 @@
         <v>399</v>
       </c>
       <c r="G9" s="3">
-        <v>2722</v>
+        <v>2962</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
@@ -2668,151 +2684,151 @@
         <v>399</v>
       </c>
       <c r="G10" s="3">
-        <v>4452</v>
+        <v>2722</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
-        <v>396</v>
+      <c r="A11" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>397</v>
+        <v>302</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G11" s="3">
-        <v>5223</v>
+        <v>4452</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="19" t="s">
-        <v>395</v>
+      <c r="A12" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>392</v>
+        <v>166</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G12" s="3">
-        <v>1458</v>
+        <v>5223</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
-        <v>381</v>
+      <c r="A13" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>384</v>
+        <v>174</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G13" s="3">
-        <v>1194</v>
+        <v>1458</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19" t="s">
-        <v>380</v>
+      <c r="A14" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G14" s="3">
-        <v>8520</v>
+        <v>1194</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="G15" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
@@ -2821,1620 +2837,1646 @@
         <v>308</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G16" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G17" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G18" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="G19" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G20" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>391</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G21" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>179</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G22" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G23" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="28" t="s">
-        <v>370</v>
+      <c r="A24" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B24" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="G24" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="19" t="s">
-        <v>369</v>
+      <c r="A25" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G25" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G26" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G27" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G28" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G29" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G30" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="G31" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>290</v>
+        <v>247</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G32" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>106</v>
+        <v>4277</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F33" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G33" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G34" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G35" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="G36" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G37" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G38" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>131</v>
+        <v>356</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G39" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G40" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G41" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G42" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G43" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G44" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G45" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G46" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G47" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G48" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>91</v>
+        <v>2009</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C49" s="19" t="s">
-        <v>33</v>
+        <v>346</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G49" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H49" s="19" t="s">
-        <v>89</v>
+        <v>2369</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B50" s="19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C50" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G50" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G51" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G52" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G53" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G54" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G55" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G56" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B57" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G57" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G58" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G59" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G60" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G61" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="G62" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G63" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G64" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G65" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F66" s="19" t="s">
         <v>215</v>
       </c>
       <c r="G66" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G67" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F68" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G68" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G69" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G70" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G71" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B72" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G72" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G73" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G74" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G75" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F76" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G76" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H76" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A77" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B77" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C77" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F76" s="19" t="s">
+      <c r="F77" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G77" s="3">
         <v>4638</v>
       </c>
-      <c r="H76" s="19" t="s">
+      <c r="H77" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A77" s="22" t="s">
+    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B77" s="22" t="s">
+      <c r="B78" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="22" t="s">
+      <c r="C78" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D78" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E77" s="4" t="s">
+      <c r="E78" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F77" s="22" t="s">
+      <c r="F78" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G77" s="5">
+      <c r="G78" s="5">
         <v>2369</v>
       </c>
-      <c r="H77" s="22" t="s">
+      <c r="H78" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="36" t="s">
+    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B78" s="37"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="37"/>
-      <c r="F78" s="38"/>
-      <c r="G78" s="11">
-        <f>SUM(G3:G77)</f>
-        <v>328311</v>
-      </c>
-      <c r="H78" s="12"/>
+      <c r="B79" s="37"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="37"/>
+      <c r="F79" s="38"/>
+      <c r="G79" s="11">
+        <f>SUM(G3:G78)</f>
+        <v>338954</v>
+      </c>
+      <c r="H79" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="A79:F79"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098E48BA-B2DB-4A6B-933B-C02D9A173B5A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EEFAB7-AB7E-4B55-884F-E547759CF8C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$80</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1710,6 +1710,18 @@
   </si>
   <si>
     <t>자돈(50~60일령) 폐사 증가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>76번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.25</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후보돈 2두 폐사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2430,7 +2442,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2484,91 +2496,91 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G3" s="3">
-        <v>10643</v>
+        <v>179</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G4" s="3">
-        <v>3500</v>
+        <v>10643</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>421</v>
+        <v>174</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>420</v>
       </c>
       <c r="G5" s="3">
-        <v>4500</v>
+        <v>3676</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
@@ -2577,24 +2589,24 @@
         <v>417</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G6" s="3">
-        <v>903</v>
+        <v>4392</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>423</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
@@ -2606,73 +2618,73 @@
         <v>417</v>
       </c>
       <c r="G7" s="3">
-        <v>3785</v>
+        <v>903</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G8" s="3">
-        <v>1951</v>
+        <v>3785</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G9" s="3">
-        <v>2962</v>
+        <v>1951</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>405</v>
+        <v>166</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
@@ -2684,21 +2696,21 @@
         <v>399</v>
       </c>
       <c r="G10" s="3">
-        <v>2722</v>
+        <v>2962</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
@@ -2710,151 +2722,151 @@
         <v>399</v>
       </c>
       <c r="G11" s="3">
-        <v>4452</v>
+        <v>2722</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="8" t="s">
-        <v>396</v>
+      <c r="A12" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>397</v>
+        <v>302</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G12" s="3">
-        <v>5223</v>
+        <v>4452</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="19" t="s">
-        <v>395</v>
+      <c r="A13" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>392</v>
+        <v>166</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G13" s="3">
-        <v>1458</v>
+        <v>5223</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
-        <v>381</v>
+      <c r="A14" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>384</v>
+        <v>174</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G14" s="3">
-        <v>1194</v>
+        <v>1458</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="19" t="s">
-        <v>380</v>
+      <c r="A15" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G15" s="3">
-        <v>8520</v>
+        <v>1194</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="G16" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
@@ -2863,1620 +2875,1646 @@
         <v>308</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G17" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G18" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G19" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="G20" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C21" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G21" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>391</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G22" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>179</v>
+        <v>391</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G23" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G24" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="28" t="s">
-        <v>370</v>
+      <c r="A25" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B25" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="G25" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="19" t="s">
-        <v>369</v>
+      <c r="A26" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G26" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G27" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G28" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G29" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G30" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G31" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B32" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="G32" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>290</v>
+        <v>247</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G33" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H33" s="8" t="s">
-        <v>106</v>
+        <v>4277</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G34" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G35" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G36" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="G37" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G38" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G39" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>131</v>
+        <v>356</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G40" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G41" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G42" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G43" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G44" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G45" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G46" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G47" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G48" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G49" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>91</v>
+        <v>2009</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C50" s="19" t="s">
-        <v>33</v>
+        <v>346</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G50" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H50" s="19" t="s">
-        <v>89</v>
+        <v>2369</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B51" s="19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G51" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G52" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G53" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G54" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G55" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G56" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G57" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B58" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G58" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G59" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G60" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G61" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G62" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="G63" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G64" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G65" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G66" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F67" s="19" t="s">
         <v>215</v>
       </c>
       <c r="G67" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G68" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F69" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G69" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G70" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G71" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G72" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G73" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G74" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G75" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G76" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B77" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F77" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G77" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H77" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A78" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C78" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F77" s="19" t="s">
+      <c r="F78" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G77" s="3">
+      <c r="G78" s="3">
         <v>4638</v>
       </c>
-      <c r="H77" s="19" t="s">
+      <c r="H78" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A78" s="22" t="s">
+    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B78" s="22" t="s">
+      <c r="B79" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C78" s="22" t="s">
+      <c r="C79" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="D79" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E79" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F78" s="22" t="s">
+      <c r="F79" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G78" s="5">
+      <c r="G79" s="5">
         <v>2369</v>
       </c>
-      <c r="H78" s="22" t="s">
+      <c r="H79" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="36" t="s">
+    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B79" s="37"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="37"/>
-      <c r="F79" s="38"/>
-      <c r="G79" s="11">
-        <f>SUM(G3:G78)</f>
-        <v>338954</v>
-      </c>
-      <c r="H79" s="12"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="38"/>
+      <c r="G80" s="11">
+        <f>SUM(G3:G79)</f>
+        <v>339201</v>
+      </c>
+      <c r="H80" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A80:F80"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0EEFAB7-AB7E-4B55-884F-E547759CF8C5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD3A5DA-793B-4DBF-8785-2B3B22ACEFEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$80</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="444">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1722,6 +1722,22 @@
   </si>
   <si>
     <t>후보돈 2두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>77번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>합천 가야면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.2.26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25~26일 모돈 3두, 자돈 25두 폐사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2442,7 +2458,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2496,117 +2512,117 @@
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A3" s="19" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>112</v>
+        <v>303</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G3" s="3">
-        <v>179</v>
+        <v>5213</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G4" s="3">
-        <v>10643</v>
+        <v>179</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G5" s="3">
-        <v>3676</v>
+        <v>10643</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>421</v>
+        <v>174</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>420</v>
       </c>
       <c r="G6" s="3">
-        <v>4392</v>
+        <v>3676</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
@@ -2615,24 +2631,24 @@
         <v>417</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G7" s="3">
-        <v>903</v>
+        <v>4392</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B8" s="19" t="s">
         <v>423</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
@@ -2644,73 +2660,73 @@
         <v>417</v>
       </c>
       <c r="G8" s="3">
-        <v>3785</v>
+        <v>903</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G9" s="3">
-        <v>1951</v>
+        <v>3785</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G10" s="3">
-        <v>2962</v>
+        <v>1951</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>405</v>
+        <v>166</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
@@ -2722,21 +2738,21 @@
         <v>399</v>
       </c>
       <c r="G11" s="3">
-        <v>2722</v>
+        <v>2962</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
@@ -2748,151 +2764,151 @@
         <v>399</v>
       </c>
       <c r="G12" s="3">
-        <v>4452</v>
+        <v>2722</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="8" t="s">
-        <v>396</v>
+      <c r="A13" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>397</v>
+        <v>302</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G13" s="3">
-        <v>5223</v>
+        <v>4452</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="19" t="s">
-        <v>395</v>
+      <c r="A14" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>392</v>
+        <v>166</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G14" s="3">
-        <v>1458</v>
+        <v>5223</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>381</v>
+      <c r="A15" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>384</v>
+        <v>174</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G15" s="3">
-        <v>1194</v>
+        <v>1458</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="19" t="s">
-        <v>380</v>
+      <c r="A16" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G16" s="3">
-        <v>8520</v>
+        <v>1194</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="G17" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
@@ -2901,1620 +2917,1646 @@
         <v>308</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G18" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G19" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G20" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="G21" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G22" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>391</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G23" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>179</v>
+        <v>391</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G24" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G25" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="28" t="s">
-        <v>370</v>
+      <c r="A26" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B26" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="G26" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="19" t="s">
-        <v>369</v>
+      <c r="A27" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G27" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G28" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B29" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G29" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G30" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G31" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G32" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B33" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="G33" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>290</v>
+        <v>247</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G34" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>106</v>
+        <v>4277</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G35" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G36" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G37" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="G38" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G39" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G40" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>131</v>
+        <v>356</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G41" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G42" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G43" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G44" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G45" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G46" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G47" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G48" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G49" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G50" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>91</v>
+        <v>2009</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C51" s="19" t="s">
-        <v>33</v>
+        <v>346</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G51" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H51" s="19" t="s">
-        <v>89</v>
+        <v>2369</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B52" s="19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G52" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G53" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G54" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G55" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G56" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G57" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G58" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B59" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G59" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G60" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G61" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G62" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G63" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="G64" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G65" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G66" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G67" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F68" s="19" t="s">
         <v>215</v>
       </c>
       <c r="G68" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G69" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F70" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G70" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G71" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G72" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G73" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B74" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G74" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G75" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G76" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G77" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B78" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F78" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G78" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H78" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A79" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C79" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E79" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F78" s="19" t="s">
+      <c r="F79" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G78" s="3">
+      <c r="G79" s="3">
         <v>4638</v>
       </c>
-      <c r="H78" s="19" t="s">
+      <c r="H79" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="22" t="s">
+    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B79" s="22" t="s">
+      <c r="B80" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C80" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D79" s="33" t="s">
+      <c r="D80" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E79" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F79" s="22" t="s">
+      <c r="F80" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G79" s="5">
+      <c r="G80" s="5">
         <v>2369</v>
       </c>
-      <c r="H79" s="22" t="s">
+      <c r="H80" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="36" t="s">
+    <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B80" s="37"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="37"/>
-      <c r="F80" s="38"/>
-      <c r="G80" s="11">
-        <f>SUM(G3:G79)</f>
-        <v>339201</v>
-      </c>
-      <c r="H80" s="12"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="37"/>
+      <c r="F81" s="38"/>
+      <c r="G81" s="11">
+        <f>SUM(G3:G80)</f>
+        <v>344414</v>
+      </c>
+      <c r="H81" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A81:F81"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD3A5DA-793B-4DBF-8785-2B3B22ACEFEB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BEAEE4-A426-4A7D-A174-27767E2665CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$82</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="449">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1738,6 +1738,26 @@
   </si>
   <si>
     <t>25~26일 모돈 3두, 자돈 25두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>72-1번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연천 군남면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026.3.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모돈(임신) 6두 폐사</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1997,7 +2017,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2115,6 +2135,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2458,7 +2481,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2515,25 +2538,25 @@
         <v>440</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="G3" s="3">
         <v>5213</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -2541,114 +2564,114 @@
         <v>437</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>112</v>
+        <v>303</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G4" s="3">
-        <v>179</v>
+        <v>5213</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="19" t="s">
-        <v>433</v>
+      <c r="A5" s="41" t="s">
+        <v>444</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G5" s="3">
-        <v>10643</v>
+        <v>172</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G6" s="3">
-        <v>3676</v>
+        <v>10643</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>421</v>
+        <v>174</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>420</v>
       </c>
       <c r="G7" s="3">
-        <v>4392</v>
+        <v>3676</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
@@ -2657,24 +2680,24 @@
         <v>417</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G8" s="3">
-        <v>903</v>
+        <v>4392</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>423</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
@@ -2686,73 +2709,73 @@
         <v>417</v>
       </c>
       <c r="G9" s="3">
-        <v>3785</v>
+        <v>903</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G10" s="3">
-        <v>1951</v>
+        <v>3785</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G11" s="3">
-        <v>2962</v>
+        <v>1951</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>405</v>
+        <v>166</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
@@ -2764,21 +2787,21 @@
         <v>399</v>
       </c>
       <c r="G12" s="3">
-        <v>2722</v>
+        <v>2962</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
@@ -2790,151 +2813,151 @@
         <v>399</v>
       </c>
       <c r="G13" s="3">
-        <v>4452</v>
+        <v>2722</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="8" t="s">
-        <v>396</v>
+      <c r="A14" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>397</v>
+        <v>302</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G14" s="3">
-        <v>5223</v>
+        <v>4452</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="19" t="s">
-        <v>395</v>
+      <c r="A15" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>392</v>
+        <v>166</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G15" s="3">
-        <v>1458</v>
+        <v>5223</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>381</v>
+      <c r="A16" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>384</v>
+        <v>174</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G16" s="3">
-        <v>1194</v>
+        <v>1458</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="19" t="s">
-        <v>380</v>
+      <c r="A17" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G17" s="3">
-        <v>8520</v>
+        <v>1194</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="G18" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
@@ -2943,1620 +2966,1646 @@
         <v>308</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G19" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G20" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G21" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="G22" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G23" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>391</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G24" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>179</v>
+        <v>391</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G25" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G26" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="28" t="s">
-        <v>370</v>
+      <c r="A27" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B27" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="G27" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="19" t="s">
-        <v>369</v>
+      <c r="A28" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G28" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G29" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B30" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G30" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G31" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G32" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G33" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="G34" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>290</v>
+        <v>247</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G35" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>106</v>
+        <v>4277</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G36" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G37" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G38" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="G39" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G40" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G41" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>131</v>
+        <v>356</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G42" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G43" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G44" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G45" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G46" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G47" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G48" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G49" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G50" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G51" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>91</v>
+        <v>2009</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C52" s="19" t="s">
-        <v>33</v>
+        <v>346</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G52" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H52" s="19" t="s">
-        <v>89</v>
+        <v>2369</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B53" s="19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G53" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G54" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G55" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G56" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G57" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G58" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G59" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B60" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G60" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G61" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G62" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G63" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G64" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="G65" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G66" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G67" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D68" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G68" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F69" s="19" t="s">
         <v>215</v>
       </c>
       <c r="G69" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G70" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F71" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G71" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G72" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G73" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G74" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B75" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G75" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G76" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G77" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G78" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D79" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E79" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F79" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H79" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E80" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F79" s="19" t="s">
+      <c r="F80" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G79" s="3">
+      <c r="G80" s="3">
         <v>4638</v>
       </c>
-      <c r="H79" s="19" t="s">
+      <c r="H80" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A80" s="22" t="s">
+    <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B80" s="22" t="s">
+      <c r="B81" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="C81" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D80" s="33" t="s">
+      <c r="D81" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E81" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F80" s="22" t="s">
+      <c r="F81" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G80" s="5">
+      <c r="G81" s="5">
         <v>2369</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H81" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="36" t="s">
+    <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B81" s="37"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="37"/>
-      <c r="F81" s="38"/>
-      <c r="G81" s="11">
-        <f>SUM(G3:G80)</f>
-        <v>344414</v>
-      </c>
-      <c r="H81" s="12"/>
+      <c r="B82" s="37"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="37"/>
+      <c r="F82" s="38"/>
+      <c r="G82" s="11">
+        <f>SUM(G4:G81)</f>
+        <v>344407</v>
+      </c>
+      <c r="H82" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A82:F82"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98BEAEE4-A426-4A7D-A174-27767E2665CC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1876C57D-F0E2-4E37-8842-235895DD1ACF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2553,7 +2553,7 @@
         <v>447</v>
       </c>
       <c r="G3" s="3">
-        <v>5213</v>
+        <v>3500</v>
       </c>
       <c r="H3" s="20" t="s">
         <v>448</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1876C57D-F0E2-4E37-8842-235895DD1ACF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22814C00-CDD8-4F48-A3D7-6975FFD0F1A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="452">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1749,15 +1749,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2026.3.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>26.3.4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>모돈(임신) 6두 폐사</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>73-1번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5일 일제검사 양성, 6일 추가검사 확진</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2119,6 +2131,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2135,9 +2150,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2481,7 +2493,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2496,16 +2508,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -2534,170 +2546,170 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="19" t="s">
-        <v>440</v>
+      <c r="A3" s="35" t="s">
+        <v>448</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>445</v>
+        <v>422</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>446</v>
+      <c r="E3" s="6">
+        <v>263.5</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G3" s="3">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="H3" s="20" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="19" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="G4" s="3">
-        <v>5213</v>
+        <v>3500</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="41" t="s">
-        <v>444</v>
+      <c r="A5" s="19" t="s">
+        <v>437</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>112</v>
+        <v>303</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G5" s="3">
-        <v>172</v>
+        <v>5213</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
-        <v>433</v>
+      <c r="A6" s="35" t="s">
+        <v>444</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="G6" s="3">
-        <v>10643</v>
+        <v>172</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G7" s="3">
-        <v>3676</v>
+        <v>10643</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="19" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>421</v>
+        <v>174</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>420</v>
       </c>
       <c r="G8" s="3">
-        <v>4392</v>
+        <v>3676</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
@@ -2706,24 +2718,24 @@
         <v>417</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G9" s="3">
-        <v>903</v>
+        <v>4392</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>423</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
@@ -2735,73 +2747,73 @@
         <v>417</v>
       </c>
       <c r="G10" s="3">
-        <v>3785</v>
+        <v>903</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G11" s="3">
-        <v>1951</v>
+        <v>3785</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>166</v>
+        <v>415</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G12" s="3">
-        <v>2962</v>
+        <v>1951</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>405</v>
+        <v>166</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
@@ -2813,21 +2825,21 @@
         <v>399</v>
       </c>
       <c r="G13" s="3">
-        <v>2722</v>
+        <v>2962</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>302</v>
+        <v>405</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
@@ -2839,151 +2851,151 @@
         <v>399</v>
       </c>
       <c r="G14" s="3">
-        <v>4452</v>
+        <v>2722</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="8" t="s">
-        <v>396</v>
+      <c r="A15" s="19" t="s">
+        <v>401</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>397</v>
+        <v>302</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>407</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G15" s="3">
-        <v>5223</v>
+        <v>4452</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="19" t="s">
-        <v>395</v>
+      <c r="A16" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>392</v>
+        <v>166</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>397</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G16" s="3">
-        <v>1458</v>
+        <v>5223</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="8" t="s">
-        <v>381</v>
+      <c r="A17" s="19" t="s">
+        <v>395</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>384</v>
+        <v>174</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G17" s="3">
-        <v>1194</v>
+        <v>1458</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="19" t="s">
-        <v>380</v>
+      <c r="A18" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>382</v>
+        <v>112</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="G18" s="3">
-        <v>8520</v>
+        <v>1194</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>306</v>
+        <v>383</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>309</v>
+        <v>386</v>
       </c>
       <c r="G19" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>313</v>
+        <v>389</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>166</v>
+        <v>303</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
@@ -2992,1620 +3004,1646 @@
         <v>308</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G20" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>390</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G21" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>312</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>178</v>
+        <v>304</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>262</v>
+        <v>307</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G22" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>181</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>261</v>
+        <v>311</v>
       </c>
       <c r="G23" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>176</v>
+        <v>173</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G24" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>391</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="G25" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>179</v>
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="G26" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G27" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="28" t="s">
-        <v>370</v>
+      <c r="A28" s="19" t="s">
+        <v>371</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>14</v>
+        <v>164</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>256</v>
+        <v>296</v>
       </c>
       <c r="G28" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="19" t="s">
-        <v>369</v>
+      <c r="A29" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F29" s="8" t="s">
-        <v>295</v>
+        <v>256</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G29" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F30" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G30" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>155</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F31" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G31" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G32" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="G33" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
       <c r="G34" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
       <c r="G35" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>290</v>
+        <v>247</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G36" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>106</v>
+        <v>4277</v>
+      </c>
+      <c r="H36" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F37" s="19" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G37" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F38" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G38" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G39" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="G40" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G41" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>286</v>
+        <v>235</v>
       </c>
       <c r="G42" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>131</v>
+        <v>356</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G43" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G44" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G45" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G46" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G47" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G48" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G49" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G50" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G51" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>34</v>
+        <v>112</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G52" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>91</v>
+        <v>2009</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" s="19" t="s">
-        <v>33</v>
+        <v>346</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G53" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>89</v>
+        <v>2369</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B54" s="19" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G54" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G55" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G56" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G57" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G58" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G59" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G60" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B61" s="19" t="s">
         <v>123</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G61" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G62" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G63" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G64" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G65" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>218</v>
+        <v>263</v>
       </c>
       <c r="G66" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G67" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G68" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D69" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G69" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F70" s="19" t="s">
         <v>215</v>
       </c>
       <c r="G70" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G71" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F72" s="19" t="s">
         <v>189</v>
       </c>
       <c r="G72" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G73" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G74" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G75" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G76" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>51</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G77" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G78" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G79" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B80" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D80" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E80" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G80" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H80" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C81" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E81" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F80" s="19" t="s">
+      <c r="F81" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G80" s="3">
+      <c r="G81" s="3">
         <v>4638</v>
       </c>
-      <c r="H80" s="19" t="s">
+      <c r="H81" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="22" t="s">
+    <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B81" s="22" t="s">
+      <c r="B82" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C81" s="22" t="s">
+      <c r="C82" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D81" s="33" t="s">
+      <c r="D82" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E81" s="4" t="s">
+      <c r="E82" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F81" s="22" t="s">
+      <c r="F82" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G81" s="5">
+      <c r="G82" s="5">
         <v>2369</v>
       </c>
-      <c r="H81" s="22" t="s">
+      <c r="H82" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="36" t="s">
+    <row r="83" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B82" s="37"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="37"/>
-      <c r="F82" s="38"/>
-      <c r="G82" s="11">
-        <f>SUM(G4:G81)</f>
+      <c r="B83" s="38"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="38"/>
+      <c r="F83" s="39"/>
+      <c r="G83" s="11">
+        <f>SUM(G5:G82)</f>
         <v>344407</v>
       </c>
-      <c r="H82" s="12"/>
+      <c r="H83" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A83:F83"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4625,18 +4663,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
@@ -5046,15 +5084,15 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" spans="2:8" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="15"/>
@@ -5069,24 +5107,24 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39" t="s">
+      <c r="D4" s="40"/>
+      <c r="E4" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39" t="s">
+      <c r="F4" s="40"/>
+      <c r="G4" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="H4" s="39"/>
+      <c r="H4" s="40"/>
     </row>
     <row r="5" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="40"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="18" t="s">
         <v>81</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22814C00-CDD8-4F48-A3D7-6975FFD0F1A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954D72AC-6957-4CBE-B0BD-3B6A802FAEAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="453">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1770,6 +1770,10 @@
   </si>
   <si>
     <t>5일 일제검사 양성, 6일 추가검사 확진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2558,8 +2562,8 @@
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E3" s="6">
-        <v>263.5</v>
+      <c r="E3" s="6" t="s">
+        <v>452</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>450</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954D72AC-6957-4CBE-B0BD-3B6A802FAEAC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F374F2D5-0817-4765-BC35-0554BE368078}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="461">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1774,6 +1774,38 @@
   </si>
   <si>
     <t>26.3.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경남</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전남</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>산청 단성면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>함평 신광면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16일 55일령 자돈 폐사 증가(일제검사 양성)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>16일 확대검사서 확진(일제검사, 지육 양성)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1874,7 +1906,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2029,11 +2061,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2154,6 +2210,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2497,7 +2559,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H83"/>
+  <dimension ref="A1:H85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2550,222 +2612,222 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="35" t="s">
-        <v>448</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>422</v>
+      <c r="A3" s="42">
+        <v>79</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="42" t="s">
+        <v>456</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>450</v>
-      </c>
-      <c r="G3" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H3" s="20" t="s">
-        <v>451</v>
+      <c r="E3" s="43" t="s">
+        <v>458</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="G3" s="42">
+        <v>2647</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>460</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="19" t="s">
-        <v>440</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>445</v>
+      <c r="A4" s="42">
+        <v>78</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>455</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>446</v>
-      </c>
-      <c r="G4" s="3">
-        <v>3500</v>
-      </c>
-      <c r="H4" s="20" t="s">
-        <v>447</v>
+      <c r="E4" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="F4" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="G4" s="42">
+        <v>5050</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="19" t="s">
-        <v>437</v>
+      <c r="A5" s="35" t="s">
+        <v>448</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>303</v>
+        <v>118</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="G5" s="3">
-        <v>5213</v>
+        <v>4300</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>443</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="35" t="s">
-        <v>444</v>
+      <c r="A6" s="19" t="s">
+        <v>440</v>
       </c>
       <c r="B6" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>425</v>
+        <v>445</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="G6" s="3">
-        <v>172</v>
+        <v>3500</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B7" s="19" t="s">
         <v>303</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="G7" s="3">
-        <v>10643</v>
+        <v>5213</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="19" t="s">
-        <v>430</v>
+      <c r="A8" s="35" t="s">
+        <v>444</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>174</v>
+        <v>112</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="G8" s="3">
-        <v>3676</v>
+        <v>172</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
-        <v>414</v>
+        <v>433</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>421</v>
+        <v>303</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
       <c r="G9" s="3">
-        <v>4392</v>
+        <v>11920</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>423</v>
+        <v>174</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G10" s="3">
-        <v>903</v>
+        <v>3676</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>170</v>
@@ -2774,102 +2836,102 @@
         <v>417</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G11" s="3">
-        <v>3785</v>
+        <v>4392</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G12" s="3">
-        <v>1951</v>
+        <v>903</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>166</v>
+        <v>423</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="G13" s="3">
-        <v>2962</v>
+        <v>3785</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>408</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="G14" s="3">
-        <v>2722</v>
+        <v>1951</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>170</v>
@@ -2881,460 +2943,460 @@
         <v>399</v>
       </c>
       <c r="G15" s="3">
-        <v>4452</v>
+        <v>2962</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="8" t="s">
-        <v>396</v>
+      <c r="A16" s="19" t="s">
+        <v>402</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>397</v>
+        <v>405</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>406</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>399</v>
       </c>
       <c r="G16" s="3">
-        <v>5223</v>
+        <v>2722</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="G17" s="3">
-        <v>1458</v>
+        <v>4452</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="G18" s="3">
-        <v>1194</v>
+        <v>5223</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>382</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>383</v>
+        <v>174</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>392</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="G19" s="3">
-        <v>8520</v>
+        <v>1458</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="19" t="s">
-        <v>379</v>
+      <c r="A20" s="8" t="s">
+        <v>381</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>303</v>
+        <v>112</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>306</v>
+        <v>384</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>309</v>
+        <v>387</v>
       </c>
       <c r="G20" s="3">
-        <v>2562</v>
+        <v>1194</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>313</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>166</v>
+        <v>382</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>305</v>
+        <v>383</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>308</v>
+        <v>386</v>
       </c>
       <c r="G21" s="3">
-        <v>4050</v>
+        <v>8520</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G22" s="3">
-        <v>18586</v>
+        <v>2562</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>178</v>
+        <v>305</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>262</v>
+        <v>308</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G23" s="3">
-        <v>21114</v>
+        <v>4050</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>181</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>177</v>
+        <v>304</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>261</v>
+        <v>307</v>
       </c>
       <c r="G24" s="3">
-        <v>7945</v>
+        <v>18586</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>180</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>176</v>
+        <v>174</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="G25" s="3">
-        <v>2459</v>
+        <v>21114</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>391</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>177</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>170</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="G26" s="3">
-        <v>20150</v>
+        <v>7945</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>167</v>
+        <v>172</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>176</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>297</v>
+        <v>260</v>
       </c>
       <c r="G27" s="3">
-        <v>1423</v>
+        <v>2459</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>168</v>
+        <v>391</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>164</v>
+        <v>171</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>175</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="G28" s="3">
-        <v>847</v>
+        <v>20150</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A29" s="28" t="s">
-        <v>370</v>
+      <c r="A29" s="19" t="s">
+        <v>372</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="D29" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="G29" s="3">
-        <v>8889</v>
+        <v>1423</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>295</v>
+        <v>257</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>296</v>
       </c>
       <c r="G30" s="3">
-        <v>2465</v>
+        <v>847</v>
       </c>
       <c r="H30" s="20" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="19" t="s">
-        <v>368</v>
+      <c r="A31" s="28" t="s">
+        <v>370</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>152</v>
+        <v>14</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F31" s="8" t="s">
-        <v>294</v>
+        <v>256</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="G31" s="3">
-        <v>5983</v>
+        <v>8889</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>251</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G32" s="3">
-        <v>4134</v>
+        <v>2465</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>152</v>
@@ -3343,414 +3405,414 @@
         <v>251</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G33" s="3">
-        <v>5232</v>
+        <v>5983</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>112</v>
+        <v>155</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="G34" s="3">
-        <v>4950</v>
+        <v>4134</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>87</v>
+        <v>251</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G35" s="3">
-        <v>2733</v>
+        <v>5232</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>110</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G36" s="3">
-        <v>4277</v>
+        <v>4950</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>290</v>
+        <v>248</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>291</v>
       </c>
       <c r="G37" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>106</v>
+        <v>2733</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>289</v>
+        <v>247</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>247</v>
       </c>
       <c r="G38" s="3">
-        <v>1927</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>104</v>
+        <v>4277</v>
+      </c>
+      <c r="H38" s="20" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G39" s="3">
-        <v>1117</v>
+        <v>4198</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G40" s="3">
-        <v>193</v>
+        <v>1927</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>236</v>
+        <v>288</v>
       </c>
       <c r="G41" s="3">
-        <v>25900</v>
+        <v>1117</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>235</v>
+        <v>287</v>
       </c>
       <c r="G42" s="3">
-        <v>1577</v>
+        <v>193</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>15</v>
+        <v>98</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>286</v>
+        <v>236</v>
       </c>
       <c r="G43" s="3">
-        <v>2375</v>
+        <v>25900</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>131</v>
+        <v>357</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>120</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>285</v>
+        <v>235</v>
       </c>
       <c r="G44" s="3">
-        <v>499</v>
+        <v>1577</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>124</v>
+        <v>356</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>127</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G45" s="3">
-        <v>1246</v>
+        <v>2375</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>250</v>
+        <v>87</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G46" s="3">
-        <v>6077</v>
+        <v>499</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D47" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G47" s="3">
-        <v>6118</v>
+        <v>1246</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G48" s="3">
-        <v>9724</v>
+        <v>6077</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C49" s="8" t="s">
         <v>69</v>
@@ -3759,895 +3821,947 @@
         <v>250</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G49" s="3">
-        <v>10218</v>
+        <v>6118</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G50" s="3">
-        <v>12842</v>
+        <v>9724</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G51" s="3">
-        <v>1956</v>
+        <v>10218</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>112</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G52" s="3">
-        <v>2009</v>
+        <v>12842</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>34</v>
+        <v>129</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G53" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>91</v>
+        <v>1956</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="B54" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="B54" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="19" t="s">
-        <v>33</v>
+      <c r="C54" s="8" t="s">
+        <v>35</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G54" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H54" s="19" t="s">
-        <v>89</v>
+        <v>2009</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B55" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="B55" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C55" s="19" t="s">
-        <v>32</v>
+      <c r="C55" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G55" s="3">
-        <v>5499</v>
-      </c>
-      <c r="H55" s="19" t="s">
-        <v>63</v>
+        <v>2369</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>38</v>
+        <v>250</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G56" s="3">
-        <v>1133</v>
+        <v>8094</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D57" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G57" s="3">
-        <v>5203</v>
+        <v>5499</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G58" s="3">
-        <v>6824</v>
+        <v>1133</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G59" s="3">
-        <v>8243</v>
+        <v>5203</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="G60" s="3">
-        <v>5614</v>
+        <v>6824</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>38</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G61" s="3">
-        <v>1175</v>
+        <v>8243</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G62" s="3">
-        <v>579</v>
+        <v>5614</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="G63" s="3">
-        <v>2300</v>
+        <v>1175</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D64" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="G64" s="3">
-        <v>1801</v>
+        <v>579</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G65" s="3">
-        <v>2387</v>
+        <v>2300</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>139</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G66" s="3">
-        <v>385</v>
+        <v>1801</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B67" s="19" t="s">
         <v>119</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="G67" s="3">
-        <v>1020</v>
+        <v>2387</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>36</v>
+        <v>139</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="G68" s="3">
-        <v>726</v>
+        <v>385</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G69" s="3">
-        <v>4245</v>
+        <v>1020</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G70" s="3">
-        <v>2916</v>
+        <v>726</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D71" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G71" s="3">
-        <v>2267</v>
+        <v>4245</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G72" s="3">
-        <v>19</v>
+        <v>2916</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B73" s="19" t="s">
         <v>112</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>189</v>
+        <v>215</v>
       </c>
       <c r="G73" s="3">
-        <v>2661</v>
+        <v>2267</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="G74" s="3">
-        <v>2123</v>
+        <v>19</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="G75" s="3">
-        <v>1125</v>
+        <v>2661</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B76" s="19" t="s">
         <v>115</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="G76" s="3">
-        <v>2</v>
+        <v>2123</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G77" s="3">
-        <v>869</v>
+        <v>1125</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="19" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G78" s="3">
-        <v>388</v>
+        <v>2</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D79" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G79" s="3">
-        <v>2273</v>
+        <v>869</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="19" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D80" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G80" s="3">
-        <v>2119</v>
+        <v>388</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="19" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E81" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F81" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="G81" s="3">
+        <v>2273</v>
+      </c>
+      <c r="H81" s="19" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A82" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C82" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D82" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F82" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H82" s="19" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="B83" s="19" t="s">
+        <v>112</v>
+      </c>
+      <c r="C83" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="F81" s="19" t="s">
+      <c r="F83" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="G81" s="3">
+      <c r="G83" s="3">
         <v>4638</v>
       </c>
-      <c r="H81" s="19" t="s">
+      <c r="H83" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="22" t="s">
+    <row r="84" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="22" t="s">
         <v>317</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B84" s="22" t="s">
         <v>112</v>
       </c>
-      <c r="C82" s="22" t="s">
+      <c r="C84" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D82" s="33" t="s">
+      <c r="D84" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E82" s="4" t="s">
+      <c r="E84" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F82" s="22" t="s">
+      <c r="F84" s="22" t="s">
         <v>192</v>
       </c>
-      <c r="G82" s="5">
+      <c r="G84" s="5">
         <v>2369</v>
       </c>
-      <c r="H82" s="22" t="s">
+      <c r="H84" s="22" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="37" t="s">
+    <row r="85" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="B83" s="38"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="38"/>
-      <c r="F83" s="39"/>
-      <c r="G83" s="11">
-        <f>SUM(G5:G82)</f>
-        <v>344407</v>
-      </c>
-      <c r="H83" s="12"/>
+      <c r="B85" s="38"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="38"/>
+      <c r="F85" s="39"/>
+      <c r="G85" s="11">
+        <f>SUM(G3:G84)</f>
+        <v>361181</v>
+      </c>
+      <c r="H85" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A85:F85"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F374F2D5-0817-4765-BC35-0554BE368078}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C9E334-E32B-4BAE-8CCA-8D04A662D885}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="462">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -106,10 +106,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>영월 주천면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>고성 간성읍</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1806,6 +1802,14 @@
   </si>
   <si>
     <t>16일 확대검사서 확진(일제검사, 지육 양성)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>79번</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2575,7 +2579,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.6" x14ac:dyDescent="0.4">
       <c r="A1" s="36" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -2590,13 +2594,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>301</v>
-      </c>
       <c r="D2" s="10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E2" s="32" t="s">
         <v>1</v>
@@ -2608,2139 +2612,2139 @@
         <v>3</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="42">
-        <v>79</v>
+      <c r="A3" s="42" t="s">
+        <v>461</v>
       </c>
       <c r="B3" s="42" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C3" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="F3" s="43" t="s">
         <v>456</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>458</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>457</v>
       </c>
       <c r="G3" s="42">
         <v>2647</v>
       </c>
       <c r="H3" s="42" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="42" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="42">
-        <v>78</v>
-      </c>
       <c r="B4" s="42" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E4" s="43" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F4" s="43" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G4" s="42">
         <v>5050</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="35" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G5" s="3">
         <v>4300</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C6" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>446</v>
       </c>
       <c r="G6" s="3">
         <v>3500</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C7" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>441</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>442</v>
-      </c>
       <c r="F7" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G7" s="3">
         <v>5213</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="35" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G8" s="3">
         <v>172</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>434</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>435</v>
-      </c>
       <c r="F9" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="G9" s="3">
         <v>11920</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G10" s="3">
         <v>3676</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>421</v>
       </c>
-      <c r="C11" s="19" t="s">
-        <v>422</v>
-      </c>
       <c r="D11" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G11" s="3">
         <v>4392</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G12" s="3">
         <v>903</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B13" s="19" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>424</v>
-      </c>
       <c r="D13" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G13" s="3">
         <v>3785</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B14" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>416</v>
-      </c>
       <c r="D14" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E14" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>418</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>419</v>
       </c>
       <c r="G14" s="3">
         <v>1951</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
+        <v>402</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>404</v>
-      </c>
       <c r="D15" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G15" s="3">
         <v>2962</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B16" s="19" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>406</v>
-      </c>
       <c r="D16" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G16" s="3">
         <v>2722</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="G17" s="3">
         <v>4452</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
+        <v>395</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
         <v>398</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>399</v>
       </c>
       <c r="G18" s="3">
         <v>5223</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="19" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="E19" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>393</v>
-      </c>
       <c r="F19" s="6" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G19" s="3">
         <v>1458</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>386</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>387</v>
       </c>
       <c r="G20" s="3">
         <v>1194</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B21" s="19" t="s">
+        <v>381</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>383</v>
-      </c>
       <c r="D21" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E21" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>385</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>386</v>
       </c>
       <c r="G21" s="3">
         <v>8520</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>308</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>309</v>
       </c>
       <c r="G22" s="3">
         <v>2562</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G23" s="3">
         <v>4050</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G24" s="3">
         <v>18586</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G25" s="3">
         <v>21114</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D26" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G26" s="3">
         <v>7945</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G27" s="3">
         <v>2459</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G28" s="3">
         <v>20150</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B29" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>167</v>
-      </c>
       <c r="D29" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="G29" s="3">
         <v>1423</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G30" s="3">
         <v>847</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="28" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C31" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G31" s="3">
         <v>8889</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="19" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>162</v>
-      </c>
       <c r="D32" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F32" s="8" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G32" s="3">
         <v>2465</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G33" s="3">
         <v>5983</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G34" s="3">
         <v>4134</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D35" s="19" t="s">
+        <v>250</v>
+      </c>
+      <c r="E35" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E35" s="6" t="s">
-        <v>252</v>
-      </c>
       <c r="F35" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G35" s="3">
         <v>5232</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G36" s="3">
         <v>4950</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G37" s="3">
         <v>2733</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G38" s="3">
         <v>4277</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="G39" s="3">
         <v>4198</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G40" s="3">
         <v>1927</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G41" s="3">
         <v>1117</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G42" s="3">
         <v>193</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G43" s="3">
         <v>25900</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G44" s="3">
         <v>1577</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C45" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="G45" s="3">
         <v>2375</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="D46" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="19" t="s">
-        <v>87</v>
-      </c>
       <c r="E46" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G46" s="3">
         <v>499</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G47" s="3">
         <v>1246</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G48" s="3">
         <v>6077</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G49" s="3">
         <v>6118</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G50" s="3">
         <v>9724</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G51" s="3">
         <v>10218</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G52" s="3">
         <v>12842</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G53" s="3">
         <v>1956</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G54" s="3">
         <v>2009</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G55" s="3">
         <v>2369</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G56" s="3">
         <v>8094</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G57" s="3">
         <v>5499</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G58" s="3">
         <v>1133</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G59" s="3">
         <v>5203</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G60" s="3">
         <v>6824</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G61" s="3">
         <v>8243</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G62" s="3">
         <v>5614</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G63" s="3">
         <v>1175</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B64" s="19" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G64" s="3">
         <v>579</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G65" s="3">
         <v>2300</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G66" s="3">
         <v>1801</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G67" s="3">
         <v>2387</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C68" s="19" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G68" s="3">
         <v>385</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C69" s="19" t="s">
         <v>20</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G69" s="3">
         <v>1020</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C70" s="19" t="s">
         <v>19</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G70" s="3">
         <v>726</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C71" s="19" t="s">
         <v>18</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G71" s="3">
         <v>4245</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C72" s="19" t="s">
         <v>17</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G72" s="3">
         <v>2916</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C73" s="19" t="s">
         <v>16</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F73" s="19" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G73" s="3">
         <v>2267</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C74" s="19" t="s">
         <v>15</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F74" s="19" t="s">
         <v>188</v>
-      </c>
-      <c r="F74" s="19" t="s">
-        <v>189</v>
       </c>
       <c r="G74" s="3">
         <v>19</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75" s="19" t="s">
         <v>14</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F75" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G75" s="3">
         <v>2661</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C76" s="19" t="s">
         <v>13</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G76" s="3">
         <v>2123</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C77" s="19" t="s">
         <v>12</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G77" s="3">
         <v>1125</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="19" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C78" s="19" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G78" s="3">
         <v>2</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C79" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G79" s="3">
         <v>869</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C80" s="19" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G80" s="3">
         <v>388</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C81" s="19" t="s">
         <v>8</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G81" s="3">
         <v>2273</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C82" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G82" s="3">
         <v>2119</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="19" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B83" s="19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C83" s="19" t="s">
         <v>6</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F83" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G83" s="3">
         <v>4638</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="84" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="22" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B84" s="22" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C84" s="22" t="s">
         <v>5</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E84" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F84" s="22" t="s">
         <v>191</v>
-      </c>
-      <c r="F84" s="22" t="s">
-        <v>192</v>
       </c>
       <c r="G84" s="5">
         <v>2369</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
@@ -4782,7 +4786,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
       <c r="A1" s="36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="36"/>
       <c r="C1" s="36"/>
@@ -4813,40 +4817,40 @@
     </row>
     <row r="3" spans="1:11" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="G3" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="H3" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="I3" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="J3" s="23" t="s">
         <v>135</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="H3" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="I3" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="J3" s="23" t="s">
-        <v>136</v>
       </c>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" ht="26.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
       <c r="A4" s="24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B4" s="24">
         <v>9</v>
@@ -4855,22 +4859,22 @@
         <v>5</v>
       </c>
       <c r="D4" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F4" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G4" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H4" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I4" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J4" s="31">
         <f t="shared" ref="J4:J10" si="0">SUM(B4:H4)</f>
@@ -4880,31 +4884,31 @@
     </row>
     <row r="5" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B5" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>148</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>149</v>
       </c>
       <c r="D5" s="25">
         <v>2</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F5" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G5" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H5" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J5" s="25">
         <f t="shared" si="0"/>
@@ -4914,31 +4918,31 @@
     </row>
     <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="25" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D6" s="25">
         <v>5</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G6" s="25" t="s">
+        <v>147</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="H6" s="25" t="s">
-        <v>149</v>
-      </c>
       <c r="I6" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J6" s="25">
         <f t="shared" si="0"/>
@@ -4948,31 +4952,31 @@
     </row>
     <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B7" s="25">
         <v>2</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D7" s="25">
         <v>5</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J7" s="25">
         <f t="shared" si="0"/>
@@ -4982,31 +4986,31 @@
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="25" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B8" s="25">
         <v>6</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" s="25">
         <v>4</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J8" s="25">
         <f t="shared" si="0"/>
@@ -5016,13 +5020,13 @@
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B9" s="24">
         <v>3</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D9" s="24">
         <v>3</v>
@@ -5031,16 +5035,16 @@
         <v>5</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H9" s="25" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J9" s="25">
         <f t="shared" si="0"/>
@@ -5050,31 +5054,31 @@
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="31" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B10" s="31">
         <v>5</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D10" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F10" s="31">
         <v>1</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H10" s="25" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J10" s="25">
         <f t="shared" si="0"/>
@@ -5084,19 +5088,19 @@
     </row>
     <row r="11" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="26" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B11" s="26">
         <v>2</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D11" s="26">
         <v>1</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F11" s="26">
         <v>1</v>
@@ -5118,7 +5122,7 @@
     </row>
     <row r="12" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B12" s="3">
         <f>SUM(B4:B11)</f>
@@ -5203,7 +5207,7 @@
     </row>
     <row r="2" spans="2:8" ht="27.6" x14ac:dyDescent="0.4">
       <c r="B2" s="36" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C2" s="36"/>
       <c r="D2" s="36"/>
@@ -5226,40 +5230,40 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" s="40" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D4" s="40"/>
       <c r="E4" s="40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F4" s="40"/>
       <c r="G4" s="40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H4" s="40"/>
     </row>
     <row r="5" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B5" s="41"/>
       <c r="C5" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>84</v>
-      </c>
       <c r="H5" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
@@ -5464,7 +5468,7 @@
     </row>
     <row r="14" spans="2:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C14" s="14">
         <f t="shared" si="0"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3C9E334-E32B-4BAE-8CCA-8D04A662D885}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F478E62-9FEC-4D89-A902-3F34AAE2433D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13,14 +13,14 @@
     <sheet name="살처분" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사육돼지!$A$2:$H$86</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="466">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1810,6 +1810,22 @@
   </si>
   <si>
     <t>79번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예살</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>홍성 홍북읍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26.3.30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>40일령 자돈 폐사 증가(2.22 혀끝 양성 이력)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2198,6 +2214,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2214,12 +2236,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2563,7 +2579,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H85"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -2578,16 +2594,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="10" t="s">
@@ -2616,248 +2632,248 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="22.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="42" t="s">
-        <v>461</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>453</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>455</v>
+      <c r="A3" s="36" t="s">
+        <v>462</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>463</v>
       </c>
       <c r="D3" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E3" s="43" t="s">
-        <v>457</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>456</v>
-      </c>
-      <c r="G3" s="42">
-        <v>2647</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>459</v>
+      <c r="E3" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4405</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="42" t="s">
-        <v>460</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="C4" s="42" t="s">
-        <v>454</v>
+      <c r="A4" s="36" t="s">
+        <v>461</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>453</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>455</v>
       </c>
       <c r="D4" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="37" t="s">
+        <v>457</v>
+      </c>
+      <c r="F4" s="37" t="s">
         <v>456</v>
       </c>
-      <c r="F4" s="43" t="s">
-        <v>456</v>
-      </c>
-      <c r="G4" s="42">
-        <v>5050</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>458</v>
+      <c r="G4" s="3">
+        <v>2647</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="35" t="s">
-        <v>447</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>421</v>
+      <c r="A5" s="36" t="s">
+        <v>460</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>452</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>454</v>
       </c>
       <c r="D5" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>449</v>
+      <c r="E5" s="37" t="s">
+        <v>456</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>456</v>
       </c>
       <c r="G5" s="3">
-        <v>4300</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>450</v>
+        <v>5050</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="19" t="s">
-        <v>439</v>
+      <c r="A6" s="35" t="s">
+        <v>447</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="G6" s="3">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="19" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D7" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="G7" s="3">
-        <v>5213</v>
+        <v>3500</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="35" t="s">
-        <v>443</v>
+      <c r="A8" s="19" t="s">
+        <v>436</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>111</v>
+        <v>302</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="D8" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="G8" s="3">
-        <v>172</v>
+        <v>5213</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="19" t="s">
-        <v>432</v>
+      <c r="A9" s="35" t="s">
+        <v>443</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>302</v>
+        <v>111</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="D9" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="G9" s="3">
-        <v>11920</v>
+        <v>172</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="19" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>419</v>
+        <v>434</v>
       </c>
       <c r="G10" s="3">
-        <v>3676</v>
+        <v>11920</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="19" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>420</v>
+        <v>173</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>419</v>
       </c>
       <c r="G11" s="3">
-        <v>4392</v>
+        <v>3676</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="19" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="D12" s="19" t="s">
         <v>169</v>
@@ -2866,24 +2882,24 @@
         <v>416</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G12" s="3">
-        <v>903</v>
+        <v>4392</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>422</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>169</v>
@@ -2895,73 +2911,73 @@
         <v>416</v>
       </c>
       <c r="G13" s="3">
-        <v>3785</v>
+        <v>903</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="19" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G14" s="3">
-        <v>1951</v>
+        <v>3785</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="19" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>165</v>
+        <v>414</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="D15" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="G15" s="3">
-        <v>2962</v>
+        <v>1951</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>404</v>
+        <v>165</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D16" s="19" t="s">
         <v>169</v>
@@ -2973,21 +2989,21 @@
         <v>398</v>
       </c>
       <c r="G16" s="3">
-        <v>2722</v>
+        <v>2962</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="19" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>301</v>
+        <v>404</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>169</v>
@@ -2999,151 +3015,151 @@
         <v>398</v>
       </c>
       <c r="G17" s="3">
-        <v>4452</v>
+        <v>2722</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="8" t="s">
-        <v>395</v>
+      <c r="A18" s="19" t="s">
+        <v>400</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>396</v>
+        <v>301</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>406</v>
       </c>
       <c r="D18" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>398</v>
       </c>
       <c r="G18" s="3">
-        <v>5223</v>
+        <v>4452</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="19" t="s">
-        <v>394</v>
+      <c r="A19" s="8" t="s">
+        <v>395</v>
       </c>
       <c r="B19" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C19" s="19" t="s">
-        <v>391</v>
+        <v>165</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>396</v>
       </c>
       <c r="D19" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="G19" s="3">
-        <v>1458</v>
+        <v>5223</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="8" t="s">
-        <v>380</v>
+      <c r="A20" s="19" t="s">
+        <v>394</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>383</v>
+        <v>173</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>391</v>
       </c>
       <c r="D20" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="G20" s="3">
-        <v>1194</v>
+        <v>1458</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="19" t="s">
-        <v>379</v>
+      <c r="A21" s="8" t="s">
+        <v>380</v>
       </c>
       <c r="B21" s="19" t="s">
-        <v>381</v>
+        <v>111</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D21" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G21" s="3">
-        <v>8520</v>
+        <v>1194</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>302</v>
+        <v>381</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>305</v>
+        <v>382</v>
       </c>
       <c r="D22" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>307</v>
+        <v>384</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>308</v>
+        <v>385</v>
       </c>
       <c r="G22" s="3">
-        <v>2562</v>
+        <v>8520</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>312</v>
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>165</v>
+        <v>302</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D23" s="19" t="s">
         <v>169</v>
@@ -3152,1165 +3168,1165 @@
         <v>307</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G23" s="3">
-        <v>4050</v>
+        <v>2562</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>389</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="19" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B24" s="19" t="s">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D24" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G24" s="3">
-        <v>18586</v>
+        <v>4050</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>311</v>
+        <v>389</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>173</v>
+        <v>301</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>177</v>
+        <v>303</v>
       </c>
       <c r="D25" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>261</v>
+        <v>306</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G25" s="3">
-        <v>21114</v>
+        <v>18586</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>180</v>
+        <v>311</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B26" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D26" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>260</v>
+        <v>310</v>
       </c>
       <c r="G26" s="3">
-        <v>7945</v>
+        <v>21114</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="19" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>175</v>
+        <v>172</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="D27" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G27" s="3">
-        <v>2459</v>
+        <v>7945</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>390</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B28" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D28" s="19" t="s">
         <v>169</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>309</v>
+        <v>259</v>
       </c>
       <c r="G28" s="3">
-        <v>20150</v>
+        <v>2459</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>178</v>
+        <v>390</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>174</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>250</v>
+        <v>169</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="G29" s="3">
-        <v>1423</v>
+        <v>20150</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B30" s="19" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="D30" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G30" s="3">
-        <v>847</v>
+        <v>1423</v>
       </c>
       <c r="H30" s="20" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="28" t="s">
-        <v>369</v>
+      <c r="A31" s="19" t="s">
+        <v>370</v>
       </c>
       <c r="B31" s="19" t="s">
         <v>111</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>14</v>
+        <v>163</v>
       </c>
       <c r="D31" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>255</v>
+        <v>295</v>
       </c>
       <c r="G31" s="3">
-        <v>8889</v>
+        <v>847</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="19" t="s">
-        <v>368</v>
+      <c r="A32" s="28" t="s">
+        <v>369</v>
       </c>
       <c r="B32" s="19" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="D32" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>294</v>
+        <v>255</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="G32" s="3">
-        <v>2465</v>
+        <v>8889</v>
       </c>
       <c r="H32" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="19" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="D33" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G33" s="3">
-        <v>5983</v>
+        <v>2465</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>154</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D34" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F34" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G34" s="3">
-        <v>4134</v>
+        <v>5983</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="19" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D35" s="19" t="s">
         <v>250</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F35" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G35" s="3">
-        <v>5232</v>
+        <v>4134</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D36" s="19" t="s">
-        <v>86</v>
+        <v>250</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F36" s="8" t="s">
-        <v>248</v>
+        <v>291</v>
       </c>
       <c r="G36" s="3">
-        <v>4950</v>
+        <v>5232</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F37" s="8" t="s">
-        <v>290</v>
+        <v>248</v>
       </c>
       <c r="G37" s="3">
-        <v>2733</v>
+        <v>4950</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="19" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>118</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D38" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F38" s="8" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
       <c r="G38" s="3">
-        <v>4277</v>
+        <v>2733</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>289</v>
+        <v>246</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>246</v>
       </c>
       <c r="G39" s="3">
-        <v>4198</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>105</v>
+        <v>4277</v>
+      </c>
+      <c r="H39" s="20" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="19" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B40" s="19" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="D40" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G40" s="3">
-        <v>1927</v>
+        <v>4198</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="19" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B41" s="19" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D41" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G41" s="3">
-        <v>1117</v>
+        <v>1927</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="19" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D42" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G42" s="3">
-        <v>193</v>
+        <v>1117</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B43" s="19" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
       <c r="G43" s="3">
-        <v>25900</v>
+        <v>193</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B44" s="19" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D44" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G44" s="3">
-        <v>1577</v>
+        <v>25900</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B45" s="19" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="D45" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>285</v>
+        <v>234</v>
       </c>
       <c r="G45" s="3">
-        <v>2375</v>
+        <v>1577</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>130</v>
+        <v>355</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>126</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D46" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G46" s="3">
-        <v>499</v>
+        <v>2375</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>249</v>
+        <v>86</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F47" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G47" s="3">
-        <v>1246</v>
+        <v>499</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="19" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="D48" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G48" s="3">
-        <v>6077</v>
+        <v>1246</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D49" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G49" s="3">
-        <v>6118</v>
+        <v>6077</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D50" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G50" s="3">
-        <v>9724</v>
+        <v>6118</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D51" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G51" s="3">
-        <v>10218</v>
+        <v>9724</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>111</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D52" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G52" s="3">
-        <v>12842</v>
+        <v>10218</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="53" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D53" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G53" s="3">
-        <v>1956</v>
+        <v>12842</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="D54" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G54" s="3">
-        <v>2009</v>
+        <v>1956</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>33</v>
+        <v>111</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="D55" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G55" s="3">
-        <v>2369</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>90</v>
+        <v>2009</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>32</v>
+        <v>345</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="D56" s="19" t="s">
         <v>249</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G56" s="3">
-        <v>8094</v>
-      </c>
-      <c r="H56" s="19" t="s">
-        <v>88</v>
+        <v>2369</v>
+      </c>
+      <c r="H56" s="9" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>37</v>
+        <v>249</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G57" s="3">
-        <v>5499</v>
+        <v>8094</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B58" s="19" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D58" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G58" s="3">
-        <v>1133</v>
+        <v>5499</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="19" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B59" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D59" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G59" s="3">
-        <v>5203</v>
+        <v>1133</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B60" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D60" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G60" s="3">
-        <v>6824</v>
+        <v>5203</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B61" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D61" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F61" s="19" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G61" s="3">
-        <v>8243</v>
+        <v>6824</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="19" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D62" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G62" s="3">
-        <v>5614</v>
+        <v>8243</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B63" s="19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D63" s="19" t="s">
         <v>37</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G63" s="3">
-        <v>1175</v>
+        <v>5614</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B64" s="19" t="s">
         <v>122</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>138</v>
+        <v>37</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G64" s="3">
-        <v>579</v>
+        <v>1175</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B65" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D65" s="19" t="s">
         <v>138</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G65" s="3">
-        <v>2300</v>
+        <v>579</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B66" s="19" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D66" s="19" t="s">
         <v>138</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F66" s="19" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G66" s="3">
-        <v>1801</v>
+        <v>2300</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B67" s="19" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D67" s="19" t="s">
         <v>138</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F67" s="19" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G67" s="3">
-        <v>2387</v>
+        <v>1801</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B68" s="19" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C68" s="19" t="s">
         <v>21</v>
@@ -4319,453 +4335,479 @@
         <v>138</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F68" s="19" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G68" s="3">
-        <v>385</v>
+        <v>2387</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="19" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B69" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>35</v>
+        <v>138</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F69" s="19" t="s">
-        <v>217</v>
+        <v>262</v>
       </c>
       <c r="G69" s="3">
-        <v>1020</v>
+        <v>385</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="19" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B70" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D70" s="19" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G70" s="3">
-        <v>726</v>
+        <v>1020</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="19" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B71" s="19" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F71" s="19" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G71" s="3">
-        <v>4245</v>
+        <v>726</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="19" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B72" s="19" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D72" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F72" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G72" s="3">
-        <v>2916</v>
+        <v>4245</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="19" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B73" s="19" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D73" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F73" s="19" t="s">
         <v>214</v>
       </c>
       <c r="G73" s="3">
-        <v>2267</v>
+        <v>2916</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B74" s="19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D74" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>188</v>
+        <v>214</v>
       </c>
       <c r="G74" s="3">
-        <v>19</v>
+        <v>2267</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="75" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B75" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D75" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F75" s="19" t="s">
         <v>188</v>
       </c>
       <c r="G75" s="3">
-        <v>2661</v>
+        <v>19</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="19" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B76" s="19" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D76" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="G76" s="3">
-        <v>2123</v>
+        <v>2661</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="19" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B77" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D77" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G77" s="3">
-        <v>1125</v>
+        <v>2123</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B78" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D78" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="G78" s="3">
-        <v>2</v>
+        <v>1125</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B79" s="19" t="s">
         <v>114</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D79" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F79" s="19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G79" s="3">
-        <v>869</v>
+        <v>2</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B80" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D80" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G80" s="3">
-        <v>388</v>
+        <v>869</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B81" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D81" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F81" s="19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G81" s="3">
-        <v>2273</v>
+        <v>388</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B82" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C82" s="19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F82" s="19" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G82" s="3">
-        <v>2119</v>
+        <v>2273</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B83" s="19" t="s">
         <v>111</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D83" s="19" t="s">
         <v>36</v>
       </c>
       <c r="E83" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F83" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2119</v>
+      </c>
+      <c r="H83" s="19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A84" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C84" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="F83" s="19" t="s">
+      <c r="F84" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="G83" s="3">
+      <c r="G84" s="3">
         <v>4638</v>
       </c>
-      <c r="H83" s="19" t="s">
+      <c r="H84" s="19" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A84" s="22" t="s">
+    <row r="85" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A85" s="22" t="s">
         <v>316</v>
       </c>
-      <c r="B84" s="22" t="s">
+      <c r="B85" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C84" s="22" t="s">
+      <c r="C85" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D84" s="33" t="s">
+      <c r="D85" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="E84" s="4" t="s">
+      <c r="E85" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="F84" s="22" t="s">
+      <c r="F85" s="22" t="s">
         <v>191</v>
       </c>
-      <c r="G84" s="5">
+      <c r="G85" s="5">
         <v>2369</v>
       </c>
-      <c r="H84" s="22" t="s">
+      <c r="H85" s="22" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A85" s="37" t="s">
+    <row r="86" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A86" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B85" s="38"/>
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="11">
-        <f>SUM(G3:G84)</f>
-        <v>361181</v>
-      </c>
-      <c r="H85" s="12"/>
+      <c r="B86" s="40"/>
+      <c r="C86" s="40"/>
+      <c r="D86" s="40"/>
+      <c r="E86" s="40"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="11">
+        <f>SUM(G3:G85)</f>
+        <v>365586</v>
+      </c>
+      <c r="H86" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="A86:F86"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -4785,18 +4827,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="36"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.4">
@@ -5206,15 +5248,15 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" spans="2:8" ht="27.6" x14ac:dyDescent="0.4">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="15"/>
@@ -5229,24 +5271,24 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="40" t="s">
+      <c r="B4" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40" t="s">
+      <c r="D4" s="42"/>
+      <c r="E4" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40" t="s">
+      <c r="F4" s="42"/>
+      <c r="G4" s="42" t="s">
         <v>79</v>
       </c>
-      <c r="H4" s="40"/>
+      <c r="H4" s="42"/>
     </row>
     <row r="5" spans="2:8" ht="18" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="41"/>
+      <c r="B5" s="43"/>
       <c r="C5" s="18" t="s">
         <v>80</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F478E62-9FEC-4D89-A902-3F34AAE2433D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB49052D-08FA-4A6C-BF7A-9E69D88A12B6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2677,7 +2677,7 @@
         <v>456</v>
       </c>
       <c r="G4" s="3">
-        <v>2647</v>
+        <v>2338</v>
       </c>
       <c r="H4" s="36" t="s">
         <v>459</v>
@@ -2703,7 +2703,7 @@
         <v>456</v>
       </c>
       <c r="G5" s="3">
-        <v>5050</v>
+        <v>5930</v>
       </c>
       <c r="H5" s="36" t="s">
         <v>458</v>
@@ -2755,7 +2755,7 @@
         <v>445</v>
       </c>
       <c r="G7" s="3">
-        <v>3500</v>
+        <v>3115</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>446</v>
@@ -2807,7 +2807,7 @@
         <v>437</v>
       </c>
       <c r="G9" s="3">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="H9" s="20" t="s">
         <v>438</v>
@@ -4800,7 +4800,7 @@
       <c r="F86" s="41"/>
       <c r="G86" s="11">
         <f>SUM(G3:G85)</f>
-        <v>365586</v>
+        <v>365777</v>
       </c>
       <c r="H86" s="12"/>
     </row>
